--- a/VerveStacks_IND_grids_kan10/SuppXLS/Scen_TSParameters_ts_01.xlsx
+++ b/VerveStacks_IND_grids_kan10/SuppXLS/Scen_TSParameters_ts_01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AC00C6C9-6D74-47F5-BBDE-15A3695BA336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C1FCB931-A931-49E6-8B7A-31CC1661700B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ev_charging_uc" sheetId="6" r:id="rId1"/>
@@ -1959,7 +1959,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F665402-536A-47F2-8673-E8E8BFEF1AF8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E14388F-4622-445B-AC9B-8700869884DB}">
   <dimension ref="A9:G11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2016,7 +2016,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F232C71-2E66-4C70-8E47-D8C72A5EB626}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A242E2B-6BCF-4666-B765-AF496ECEBFFD}">
   <dimension ref="B9:O88"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -4262,7 +4262,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{275A887A-32A9-42F7-9DC0-A5C3DE2D72BC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{576129C5-2D22-4225-B7C8-7E5D71522E41}">
   <dimension ref="B9:T179"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -9296,7 +9296,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7023FAAA-54C8-424A-9990-D1F2F4E2A0AC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9002DE7-CAE2-4664-AFB1-C38D4C98EED9}">
   <dimension ref="A9:S39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -9424,7 +9424,7 @@
         <v>37</v>
       </c>
       <c r="R12">
-        <v>0.39017483580399914</v>
+        <v>0.39017483580399909</v>
       </c>
       <c r="S12" t="s">
         <v>405</v>
@@ -9452,7 +9452,7 @@
         <v>37</v>
       </c>
       <c r="R14">
-        <v>0.46044166666666658</v>
+        <v>0.46044166666666664</v>
       </c>
       <c r="S14" t="s">
         <v>405</v>
@@ -9536,7 +9536,7 @@
         <v>37</v>
       </c>
       <c r="R20">
-        <v>0.39324999999999993</v>
+        <v>0.39325000000000004</v>
       </c>
       <c r="S20" t="s">
         <v>405</v>
@@ -9592,7 +9592,7 @@
         <v>37</v>
       </c>
       <c r="R24">
-        <v>0.38849166666666668</v>
+        <v>0.38849166666666662</v>
       </c>
       <c r="S24" t="s">
         <v>405</v>
@@ -9606,7 +9606,7 @@
         <v>37</v>
       </c>
       <c r="R25">
-        <v>0.38614999999999994</v>
+        <v>0.38614999999999999</v>
       </c>
       <c r="S25" t="s">
         <v>405</v>
@@ -9634,7 +9634,7 @@
         <v>37</v>
       </c>
       <c r="R27">
-        <v>0.4131749999999999</v>
+        <v>0.41317500000000001</v>
       </c>
       <c r="S27" t="s">
         <v>405</v>
@@ -9690,7 +9690,7 @@
         <v>37</v>
       </c>
       <c r="R31">
-        <v>0.3230083333333334</v>
+        <v>0.32300833333333334</v>
       </c>
       <c r="S31" t="s">
         <v>405</v>
@@ -9718,7 +9718,7 @@
         <v>37</v>
       </c>
       <c r="R33">
-        <v>0.33240000000000003</v>
+        <v>0.33239999999999997</v>
       </c>
       <c r="S33" t="s">
         <v>405</v>
@@ -9732,7 +9732,7 @@
         <v>37</v>
       </c>
       <c r="R34">
-        <v>0.39241666666666664</v>
+        <v>0.39241666666666669</v>
       </c>
       <c r="S34" t="s">
         <v>405</v>
@@ -9760,7 +9760,7 @@
         <v>37</v>
       </c>
       <c r="R36">
-        <v>0.39891666666666664</v>
+        <v>0.39891666666666659</v>
       </c>
       <c r="S36" t="s">
         <v>405</v>
@@ -9774,7 +9774,7 @@
         <v>37</v>
       </c>
       <c r="R37">
-        <v>0.3975833333333334</v>
+        <v>0.39758333333333334</v>
       </c>
       <c r="S37" t="s">
         <v>405</v>

--- a/VerveStacks_IND_grids_kan10/SuppXLS/Scen_TSParameters_ts_01.xlsx
+++ b/VerveStacks_IND_grids_kan10/SuppXLS/Scen_TSParameters_ts_01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C1FCB931-A931-49E6-8B7A-31CC1661700B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D318D27D-35CF-40F3-A444-A98761FAB374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ev_charging_uc" sheetId="6" r:id="rId1"/>
@@ -19,9 +19,6 @@
     <sheet name="firmness" sheetId="9" r:id="rId4"/>
     <sheet name="load_demand_peak_hydro" sheetId="10" r:id="rId5"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId6"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -40,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1698" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1699" uniqueCount="406">
   <si>
     <t>share of charging at night</t>
   </si>
@@ -1397,19 +1394,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Veda"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1733,9 +1717,8 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="str">
-        <f>IFERROR([1]Veda!D5,"ts_01")</f>
-        <v>ts_01</v>
+      <c r="A10" t="s">
+        <v>40</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5" t="s">
@@ -1959,7 +1942,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E14388F-4622-445B-AC9B-8700869884DB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6101CFDE-5D1C-4236-8027-11351340AF0A}">
   <dimension ref="A9:G11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1990,10 +1973,6 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="str">
-        <f>IFERROR(IF([1]Veda!D5=A10,"ok","x"),"")</f>
-        <v/>
-      </c>
       <c r="C11" t="s">
         <v>37</v>
       </c>
@@ -2016,7 +1995,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A242E2B-6BCF-4666-B765-AF496ECEBFFD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31C2B69B-0871-4944-A600-A73360C081EE}">
   <dimension ref="B9:O88"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -4262,7 +4241,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{576129C5-2D22-4225-B7C8-7E5D71522E41}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD1436AC-4243-4C71-ADF9-4F1BAC270B7A}">
   <dimension ref="B9:T179"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -9296,7 +9275,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9002DE7-CAE2-4664-AFB1-C38D4C98EED9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBF0ED25-9287-4C0F-B385-1FD823CCE031}">
   <dimension ref="A9:S39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -9366,10 +9345,6 @@
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A11" t="str">
-        <f>IFERROR(IF([1]Veda!D5=A10,"ok","x"),"")</f>
-        <v/>
-      </c>
       <c r="C11">
         <v>1</v>
       </c>
@@ -9404,7 +9379,7 @@
         <v>37</v>
       </c>
       <c r="R11">
-        <v>0.40393549374487786</v>
+        <v>0.40393549374487797</v>
       </c>
       <c r="S11" t="s">
         <v>405</v>
@@ -9508,7 +9483,7 @@
         <v>37</v>
       </c>
       <c r="R18">
-        <v>0.38215833333333332</v>
+        <v>0.38215833333333321</v>
       </c>
       <c r="S18" t="s">
         <v>405</v>
@@ -9606,7 +9581,7 @@
         <v>37</v>
       </c>
       <c r="R25">
-        <v>0.38614999999999999</v>
+        <v>0.38614999999999994</v>
       </c>
       <c r="S25" t="s">
         <v>405</v>
@@ -9648,7 +9623,7 @@
         <v>37</v>
       </c>
       <c r="R28">
-        <v>0.38524166666666665</v>
+        <v>0.3852416666666667</v>
       </c>
       <c r="S28" t="s">
         <v>405</v>
@@ -9718,7 +9693,7 @@
         <v>37</v>
       </c>
       <c r="R33">
-        <v>0.33239999999999997</v>
+        <v>0.33240000000000008</v>
       </c>
       <c r="S33" t="s">
         <v>405</v>
@@ -9732,7 +9707,7 @@
         <v>37</v>
       </c>
       <c r="R34">
-        <v>0.39241666666666669</v>
+        <v>0.39241666666666664</v>
       </c>
       <c r="S34" t="s">
         <v>405</v>
@@ -9774,7 +9749,7 @@
         <v>37</v>
       </c>
       <c r="R37">
-        <v>0.39758333333333334</v>
+        <v>0.3975833333333334</v>
       </c>
       <c r="S37" t="s">
         <v>405</v>
@@ -9802,7 +9777,7 @@
         <v>37</v>
       </c>
       <c r="R39">
-        <v>0.39781666666666665</v>
+        <v>0.39781666666666671</v>
       </c>
       <c r="S39" t="s">
         <v>405</v>

--- a/VerveStacks_IND_grids_kan10/SuppXLS/Scen_TSParameters_ts_01.xlsx
+++ b/VerveStacks_IND_grids_kan10/SuppXLS/Scen_TSParameters_ts_01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D318D27D-35CF-40F3-A444-A98761FAB374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9786DAD8-4005-4B51-8C6F-FEEEDDBEF1D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1942,7 +1942,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6101CFDE-5D1C-4236-8027-11351340AF0A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24965B9D-8B44-4257-B728-0F37CCA2652B}">
   <dimension ref="A9:G11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1995,7 +1995,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31C2B69B-0871-4944-A600-A73360C081EE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50E79AF4-85F1-4FFB-817C-22FC3C0E276F}">
   <dimension ref="B9:O88"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -4241,7 +4241,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD1436AC-4243-4C71-ADF9-4F1BAC270B7A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90122CEF-754C-4C04-97A4-74AECC8987C3}">
   <dimension ref="B9:T179"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -9275,7 +9275,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBF0ED25-9287-4C0F-B385-1FD823CCE031}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32F8E0C8-1A13-4D9B-BE23-EDAF2C18B2A8}">
   <dimension ref="A9:S39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -9379,7 +9379,7 @@
         <v>37</v>
       </c>
       <c r="R11">
-        <v>0.40393549374487797</v>
+        <v>0.40393549374487786</v>
       </c>
       <c r="S11" t="s">
         <v>405</v>
@@ -9413,7 +9413,7 @@
         <v>37</v>
       </c>
       <c r="R13">
-        <v>0.42094203276503689</v>
+        <v>0.420942032765037</v>
       </c>
       <c r="S13" t="s">
         <v>405</v>
@@ -9441,7 +9441,7 @@
         <v>37</v>
       </c>
       <c r="R15">
-        <v>0.44534166666666669</v>
+        <v>0.44534166666666675</v>
       </c>
       <c r="S15" t="s">
         <v>405</v>
@@ -9455,7 +9455,7 @@
         <v>37</v>
       </c>
       <c r="R16">
-        <v>0.43370833333333331</v>
+        <v>0.43370833333333336</v>
       </c>
       <c r="S16" t="s">
         <v>405</v>
@@ -9483,7 +9483,7 @@
         <v>37</v>
       </c>
       <c r="R18">
-        <v>0.38215833333333321</v>
+        <v>0.38215833333333332</v>
       </c>
       <c r="S18" t="s">
         <v>405</v>
@@ -9497,7 +9497,7 @@
         <v>37</v>
       </c>
       <c r="R19">
-        <v>0.39528333333333326</v>
+        <v>0.39528333333333338</v>
       </c>
       <c r="S19" t="s">
         <v>405</v>
@@ -9511,7 +9511,7 @@
         <v>37</v>
       </c>
       <c r="R20">
-        <v>0.39325000000000004</v>
+        <v>0.39324999999999993</v>
       </c>
       <c r="S20" t="s">
         <v>405</v>
@@ -9525,7 +9525,7 @@
         <v>37</v>
       </c>
       <c r="R21">
-        <v>0.38550833333333334</v>
+        <v>0.3855083333333334</v>
       </c>
       <c r="S21" t="s">
         <v>405</v>
@@ -9539,7 +9539,7 @@
         <v>37</v>
       </c>
       <c r="R22">
-        <v>0.40385833333333337</v>
+        <v>0.40385833333333343</v>
       </c>
       <c r="S22" t="s">
         <v>405</v>
@@ -9567,7 +9567,7 @@
         <v>37</v>
       </c>
       <c r="R24">
-        <v>0.38849166666666662</v>
+        <v>0.38849166666666668</v>
       </c>
       <c r="S24" t="s">
         <v>405</v>
@@ -9581,7 +9581,7 @@
         <v>37</v>
       </c>
       <c r="R25">
-        <v>0.38614999999999994</v>
+        <v>0.38614999999999999</v>
       </c>
       <c r="S25" t="s">
         <v>405</v>
@@ -9623,7 +9623,7 @@
         <v>37</v>
       </c>
       <c r="R28">
-        <v>0.3852416666666667</v>
+        <v>0.38524166666666665</v>
       </c>
       <c r="S28" t="s">
         <v>405</v>
@@ -9665,7 +9665,7 @@
         <v>37</v>
       </c>
       <c r="R31">
-        <v>0.32300833333333334</v>
+        <v>0.32300833333333329</v>
       </c>
       <c r="S31" t="s">
         <v>405</v>
@@ -9679,7 +9679,7 @@
         <v>37</v>
       </c>
       <c r="R32">
-        <v>0.33950833333333336</v>
+        <v>0.3395083333333333</v>
       </c>
       <c r="S32" t="s">
         <v>405</v>
@@ -9693,7 +9693,7 @@
         <v>37</v>
       </c>
       <c r="R33">
-        <v>0.33240000000000008</v>
+        <v>0.33240000000000003</v>
       </c>
       <c r="S33" t="s">
         <v>405</v>
@@ -9749,7 +9749,7 @@
         <v>37</v>
       </c>
       <c r="R37">
-        <v>0.3975833333333334</v>
+        <v>0.39758333333333334</v>
       </c>
       <c r="S37" t="s">
         <v>405</v>
@@ -9777,7 +9777,7 @@
         <v>37</v>
       </c>
       <c r="R39">
-        <v>0.39781666666666671</v>
+        <v>0.39781666666666665</v>
       </c>
       <c r="S39" t="s">
         <v>405</v>

--- a/VerveStacks_IND_grids_kan10/SuppXLS/Scen_TSParameters_ts_01.xlsx
+++ b/VerveStacks_IND_grids_kan10/SuppXLS/Scen_TSParameters_ts_01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9786DAD8-4005-4B51-8C6F-FEEEDDBEF1D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E82AC8B1-021C-47D0-8FEF-9332F0DBD3DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1699" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1690" uniqueCount="404">
   <si>
     <t>share of charging at night</t>
   </si>
@@ -612,9 +612,6 @@
     <t>elc_won_IND_066</t>
   </si>
   <si>
-    <t>elc_won_IND_067</t>
-  </si>
-  <si>
     <t>elc_wof_IND_001</t>
   </si>
   <si>
@@ -1189,9 +1186,6 @@
   </si>
   <si>
     <t>distr_wonelc_won_IND_066</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_067</t>
   </si>
   <si>
     <t>distr_sol*</t>
@@ -1722,7 +1716,7 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D10" t="s">
         <v>40</v>
@@ -1731,7 +1725,7 @@
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B11" s="5"/>
       <c r="C11" s="5" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D11" t="s">
         <v>46</v>
@@ -1740,7 +1734,7 @@
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B12" s="5"/>
       <c r="C12" s="5" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D12" t="s">
         <v>46</v>
@@ -1942,7 +1936,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24965B9D-8B44-4257-B728-0F37CCA2652B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{887B88C3-C7EF-43CE-914D-5B9B66C0E170}">
   <dimension ref="A9:G11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1995,7 +1989,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50E79AF4-85F1-4FFB-817C-22FC3C0E276F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CEF684A-4BAD-4EF5-B770-E2C9198B88BC}">
   <dimension ref="B9:O88"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2059,7 +2053,7 @@
         <v>46</v>
       </c>
       <c r="D11">
-        <v>1.000000000000004</v>
+        <v>1.0000000000000009</v>
       </c>
       <c r="E11" t="s">
         <v>47</v>
@@ -2071,19 +2065,19 @@
         <v>46</v>
       </c>
       <c r="I11">
-        <v>0.99999999999999845</v>
+        <v>1.0000000000000024</v>
       </c>
       <c r="J11" t="s">
         <v>47</v>
       </c>
       <c r="L11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="M11" t="s">
         <v>46</v>
       </c>
       <c r="N11">
-        <v>0.99999999999999967</v>
+        <v>0.99999999999999889</v>
       </c>
       <c r="O11" t="s">
         <v>47</v>
@@ -2097,7 +2091,7 @@
         <v>46</v>
       </c>
       <c r="D12">
-        <v>0.99999999999999734</v>
+        <v>0.99999999999999745</v>
       </c>
       <c r="E12" t="s">
         <v>47</v>
@@ -2109,19 +2103,19 @@
         <v>46</v>
       </c>
       <c r="I12">
-        <v>1.0000000000000013</v>
+        <v>0.99999999999999978</v>
       </c>
       <c r="J12" t="s">
         <v>47</v>
       </c>
       <c r="L12" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="M12" t="s">
         <v>46</v>
       </c>
       <c r="N12">
-        <v>1.0000000000000016</v>
+        <v>0.99999999999999656</v>
       </c>
       <c r="O12" t="s">
         <v>47</v>
@@ -2135,7 +2129,7 @@
         <v>46</v>
       </c>
       <c r="D13">
-        <v>0.99999999999999933</v>
+        <v>0.99999999999999889</v>
       </c>
       <c r="E13" t="s">
         <v>47</v>
@@ -2147,19 +2141,19 @@
         <v>46</v>
       </c>
       <c r="I13">
-        <v>0.99999999999999634</v>
+        <v>0.99999999999999889</v>
       </c>
       <c r="J13" t="s">
         <v>47</v>
       </c>
       <c r="L13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="M13" t="s">
         <v>46</v>
       </c>
       <c r="N13">
-        <v>1.0000000000000031</v>
+        <v>1.0000000000000011</v>
       </c>
       <c r="O13" t="s">
         <v>47</v>
@@ -2173,7 +2167,7 @@
         <v>46</v>
       </c>
       <c r="D14">
-        <v>0.99999999999999911</v>
+        <v>1.0000000000000016</v>
       </c>
       <c r="E14" t="s">
         <v>47</v>
@@ -2185,19 +2179,19 @@
         <v>46</v>
       </c>
       <c r="I14">
-        <v>0.99999999999999656</v>
+        <v>0.99999999999999811</v>
       </c>
       <c r="J14" t="s">
         <v>47</v>
       </c>
       <c r="L14" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="M14" t="s">
         <v>46</v>
       </c>
       <c r="N14">
-        <v>1.0000000000000056</v>
+        <v>0.99999999999999722</v>
       </c>
       <c r="O14" t="s">
         <v>47</v>
@@ -2211,7 +2205,7 @@
         <v>46</v>
       </c>
       <c r="D15">
-        <v>1.0000000000000018</v>
+        <v>1.0000000000000011</v>
       </c>
       <c r="E15" t="s">
         <v>47</v>
@@ -2223,19 +2217,19 @@
         <v>46</v>
       </c>
       <c r="I15">
-        <v>0.99999999999999978</v>
+        <v>1.0000000000000007</v>
       </c>
       <c r="J15" t="s">
         <v>47</v>
       </c>
       <c r="L15" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="M15" t="s">
         <v>46</v>
       </c>
       <c r="N15">
-        <v>0.99999999999999778</v>
+        <v>0.99999999999999478</v>
       </c>
       <c r="O15" t="s">
         <v>47</v>
@@ -2249,7 +2243,7 @@
         <v>46</v>
       </c>
       <c r="D16">
-        <v>1.0000000000000009</v>
+        <v>1</v>
       </c>
       <c r="E16" t="s">
         <v>47</v>
@@ -2261,19 +2255,19 @@
         <v>46</v>
       </c>
       <c r="I16">
-        <v>1.0000000000000011</v>
+        <v>0.99999999999999767</v>
       </c>
       <c r="J16" t="s">
         <v>47</v>
       </c>
       <c r="L16" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M16" t="s">
         <v>46</v>
       </c>
       <c r="N16">
-        <v>1.0000000000000033</v>
+        <v>0.99999999999999956</v>
       </c>
       <c r="O16" t="s">
         <v>47</v>
@@ -2287,7 +2281,7 @@
         <v>46</v>
       </c>
       <c r="D17">
-        <v>0.99999999999999689</v>
+        <v>1.0000000000000031</v>
       </c>
       <c r="E17" t="s">
         <v>47</v>
@@ -2299,19 +2293,19 @@
         <v>46</v>
       </c>
       <c r="I17">
-        <v>1.0000000000000016</v>
+        <v>0.99999999999999978</v>
       </c>
       <c r="J17" t="s">
         <v>47</v>
       </c>
       <c r="L17" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="M17" t="s">
         <v>46</v>
       </c>
       <c r="N17">
-        <v>1.0000000000000029</v>
+        <v>1.0000000000000031</v>
       </c>
       <c r="O17" t="s">
         <v>47</v>
@@ -2325,7 +2319,7 @@
         <v>46</v>
       </c>
       <c r="D18">
-        <v>0.99999999999999911</v>
+        <v>1.0000000000000033</v>
       </c>
       <c r="E18" t="s">
         <v>47</v>
@@ -2337,19 +2331,19 @@
         <v>46</v>
       </c>
       <c r="I18">
-        <v>0.99999999999999512</v>
+        <v>0.99999999999999922</v>
       </c>
       <c r="J18" t="s">
         <v>47</v>
       </c>
       <c r="L18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M18" t="s">
         <v>46</v>
       </c>
       <c r="N18">
-        <v>0.99999999999999778</v>
+        <v>1.0000000000000022</v>
       </c>
       <c r="O18" t="s">
         <v>47</v>
@@ -2363,7 +2357,7 @@
         <v>46</v>
       </c>
       <c r="D19">
-        <v>1.000000000000002</v>
+        <v>1.0000000000000004</v>
       </c>
       <c r="E19" t="s">
         <v>47</v>
@@ -2375,19 +2369,19 @@
         <v>46</v>
       </c>
       <c r="I19">
-        <v>0.99999999999999833</v>
+        <v>1</v>
       </c>
       <c r="J19" t="s">
         <v>47</v>
       </c>
       <c r="L19" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="M19" t="s">
         <v>46</v>
       </c>
       <c r="N19">
-        <v>0.99999999999999478</v>
+        <v>1.0000000000000016</v>
       </c>
       <c r="O19" t="s">
         <v>47</v>
@@ -2401,7 +2395,7 @@
         <v>46</v>
       </c>
       <c r="D20">
-        <v>0.99999999999999767</v>
+        <v>1.0000000000000007</v>
       </c>
       <c r="E20" t="s">
         <v>47</v>
@@ -2413,19 +2407,19 @@
         <v>46</v>
       </c>
       <c r="I20">
-        <v>0.99999999999999645</v>
+        <v>0.99999999999999711</v>
       </c>
       <c r="J20" t="s">
         <v>47</v>
       </c>
       <c r="L20" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="M20" t="s">
         <v>46</v>
       </c>
       <c r="N20">
-        <v>1.0000000000000038</v>
+        <v>1.0000000000000004</v>
       </c>
       <c r="O20" t="s">
         <v>47</v>
@@ -2439,7 +2433,7 @@
         <v>46</v>
       </c>
       <c r="D21">
-        <v>0.99999999999999933</v>
+        <v>0.99999999999999822</v>
       </c>
       <c r="E21" t="s">
         <v>47</v>
@@ -2451,19 +2445,19 @@
         <v>46</v>
       </c>
       <c r="I21">
-        <v>0.99999999999999778</v>
+        <v>1.0000000000000007</v>
       </c>
       <c r="J21" t="s">
         <v>47</v>
       </c>
       <c r="L21" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M21" t="s">
         <v>46</v>
       </c>
       <c r="N21">
-        <v>0.99999999999999911</v>
+        <v>0.99999999999999789</v>
       </c>
       <c r="O21" t="s">
         <v>47</v>
@@ -2477,7 +2471,7 @@
         <v>46</v>
       </c>
       <c r="D22">
-        <v>1.0000000000000009</v>
+        <v>1.0000000000000013</v>
       </c>
       <c r="E22" t="s">
         <v>47</v>
@@ -2489,19 +2483,19 @@
         <v>46</v>
       </c>
       <c r="I22">
-        <v>1.0000000000000016</v>
+        <v>0.999999999999999</v>
       </c>
       <c r="J22" t="s">
         <v>47</v>
       </c>
       <c r="L22" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M22" t="s">
         <v>46</v>
       </c>
       <c r="N22">
-        <v>1.0000000000000044</v>
+        <v>0.999999999999998</v>
       </c>
       <c r="O22" t="s">
         <v>47</v>
@@ -2515,7 +2509,7 @@
         <v>46</v>
       </c>
       <c r="D23">
-        <v>1.0000000000000011</v>
+        <v>0.99999999999999856</v>
       </c>
       <c r="E23" t="s">
         <v>47</v>
@@ -2527,19 +2521,19 @@
         <v>46</v>
       </c>
       <c r="I23">
-        <v>0.99999999999999822</v>
+        <v>0.99999999999999489</v>
       </c>
       <c r="J23" t="s">
         <v>47</v>
       </c>
       <c r="L23" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="M23" t="s">
         <v>46</v>
       </c>
       <c r="N23">
-        <v>0.99999999999999822</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="O23" t="s">
         <v>47</v>
@@ -2553,7 +2547,7 @@
         <v>46</v>
       </c>
       <c r="D24">
-        <v>0.99999999999999833</v>
+        <v>1.0000000000000029</v>
       </c>
       <c r="E24" t="s">
         <v>47</v>
@@ -2565,19 +2559,19 @@
         <v>46</v>
       </c>
       <c r="I24">
-        <v>1.0000000000000009</v>
+        <v>0.99999999999999489</v>
       </c>
       <c r="J24" t="s">
         <v>47</v>
       </c>
       <c r="L24" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M24" t="s">
         <v>46</v>
       </c>
       <c r="N24">
-        <v>0.99999999999999867</v>
+        <v>0.99999999999999967</v>
       </c>
       <c r="O24" t="s">
         <v>47</v>
@@ -2591,7 +2585,7 @@
         <v>46</v>
       </c>
       <c r="D25">
-        <v>1.000000000000002</v>
+        <v>0.99999999999999822</v>
       </c>
       <c r="E25" t="s">
         <v>47</v>
@@ -2603,19 +2597,19 @@
         <v>46</v>
       </c>
       <c r="I25">
-        <v>1.0000000000000011</v>
+        <v>1</v>
       </c>
       <c r="J25" t="s">
         <v>47</v>
       </c>
       <c r="L25" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="M25" t="s">
         <v>46</v>
       </c>
       <c r="N25">
-        <v>0.99999999999999944</v>
+        <v>0.99999999999999778</v>
       </c>
       <c r="O25" t="s">
         <v>47</v>
@@ -2629,7 +2623,7 @@
         <v>46</v>
       </c>
       <c r="D26">
-        <v>0.999999999999998</v>
+        <v>0.99999999999999889</v>
       </c>
       <c r="E26" t="s">
         <v>47</v>
@@ -2641,19 +2635,19 @@
         <v>46</v>
       </c>
       <c r="I26">
-        <v>1.000000000000004</v>
+        <v>1.0000000000000011</v>
       </c>
       <c r="J26" t="s">
         <v>47</v>
       </c>
       <c r="L26" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="M26" t="s">
         <v>46</v>
       </c>
       <c r="N26">
-        <v>0.99999999999999878</v>
+        <v>1.0000000000000022</v>
       </c>
       <c r="O26" t="s">
         <v>47</v>
@@ -2667,7 +2661,7 @@
         <v>46</v>
       </c>
       <c r="D27">
-        <v>0.99999999999999611</v>
+        <v>0.99999999999999956</v>
       </c>
       <c r="E27" t="s">
         <v>47</v>
@@ -2679,19 +2673,19 @@
         <v>46</v>
       </c>
       <c r="I27">
-        <v>0.99999999999999689</v>
+        <v>1.0000000000000004</v>
       </c>
       <c r="J27" t="s">
         <v>47</v>
       </c>
       <c r="L27" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="M27" t="s">
         <v>46</v>
       </c>
       <c r="N27">
-        <v>1.0000000000000053</v>
+        <v>1.0000000000000011</v>
       </c>
       <c r="O27" t="s">
         <v>47</v>
@@ -2705,7 +2699,7 @@
         <v>46</v>
       </c>
       <c r="D28">
-        <v>0.99999999999999944</v>
+        <v>0.99999999999999989</v>
       </c>
       <c r="E28" t="s">
         <v>47</v>
@@ -2723,13 +2717,13 @@
         <v>47</v>
       </c>
       <c r="L28" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="M28" t="s">
         <v>46</v>
       </c>
       <c r="N28">
-        <v>0.99999999999999944</v>
+        <v>0.99999999999999989</v>
       </c>
       <c r="O28" t="s">
         <v>47</v>
@@ -2743,7 +2737,7 @@
         <v>46</v>
       </c>
       <c r="D29">
-        <v>0.99999999999999845</v>
+        <v>1.0000000000000016</v>
       </c>
       <c r="E29" t="s">
         <v>47</v>
@@ -2755,19 +2749,19 @@
         <v>46</v>
       </c>
       <c r="I29">
-        <v>0.99999999999999667</v>
+        <v>1.0000000000000044</v>
       </c>
       <c r="J29" t="s">
         <v>47</v>
       </c>
       <c r="L29" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="M29" t="s">
         <v>46</v>
       </c>
       <c r="N29">
-        <v>0.999999999999999</v>
+        <v>1.000000000000002</v>
       </c>
       <c r="O29" t="s">
         <v>47</v>
@@ -2781,7 +2775,7 @@
         <v>46</v>
       </c>
       <c r="D30">
-        <v>1.0000000000000004</v>
+        <v>1.0000000000000011</v>
       </c>
       <c r="E30" t="s">
         <v>47</v>
@@ -2793,19 +2787,19 @@
         <v>46</v>
       </c>
       <c r="I30">
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="J30" t="s">
         <v>47</v>
       </c>
       <c r="L30" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M30" t="s">
         <v>46</v>
       </c>
       <c r="N30">
-        <v>0.99999999999999589</v>
+        <v>0.99999999999999922</v>
       </c>
       <c r="O30" t="s">
         <v>47</v>
@@ -2819,7 +2813,7 @@
         <v>46</v>
       </c>
       <c r="D31">
-        <v>1.0000000000000004</v>
+        <v>1.0000000000000011</v>
       </c>
       <c r="E31" t="s">
         <v>47</v>
@@ -2831,19 +2825,19 @@
         <v>46</v>
       </c>
       <c r="I31">
-        <v>0.99999999999999822</v>
+        <v>1.0000000000000009</v>
       </c>
       <c r="J31" t="s">
         <v>47</v>
       </c>
       <c r="L31" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="M31" t="s">
         <v>46</v>
       </c>
       <c r="N31">
-        <v>1</v>
+        <v>1.000000000000002</v>
       </c>
       <c r="O31" t="s">
         <v>47</v>
@@ -2857,7 +2851,7 @@
         <v>46</v>
       </c>
       <c r="D32">
-        <v>0.99999999999999978</v>
+        <v>0.99999999999999867</v>
       </c>
       <c r="E32" t="s">
         <v>47</v>
@@ -2869,19 +2863,19 @@
         <v>46</v>
       </c>
       <c r="I32">
-        <v>1.0000000000000011</v>
+        <v>0.999999999999999</v>
       </c>
       <c r="J32" t="s">
         <v>47</v>
       </c>
       <c r="L32" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="M32" t="s">
         <v>46</v>
       </c>
       <c r="N32">
-        <v>1.0000000000000027</v>
+        <v>0.99999999999999967</v>
       </c>
       <c r="O32" t="s">
         <v>47</v>
@@ -2895,7 +2889,7 @@
         <v>46</v>
       </c>
       <c r="D33">
-        <v>0.99999999999999567</v>
+        <v>1.0000000000000009</v>
       </c>
       <c r="E33" t="s">
         <v>47</v>
@@ -2907,19 +2901,19 @@
         <v>46</v>
       </c>
       <c r="I33">
-        <v>0.99999999999999967</v>
+        <v>1.0000000000000095</v>
       </c>
       <c r="J33" t="s">
         <v>47</v>
       </c>
       <c r="L33" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M33" t="s">
         <v>46</v>
       </c>
       <c r="N33">
-        <v>1.0000000000000011</v>
+        <v>0.99999999999999689</v>
       </c>
       <c r="O33" t="s">
         <v>47</v>
@@ -2933,7 +2927,7 @@
         <v>46</v>
       </c>
       <c r="D34">
-        <v>1</v>
+        <v>0.99999999999999933</v>
       </c>
       <c r="E34" t="s">
         <v>47</v>
@@ -2945,19 +2939,19 @@
         <v>46</v>
       </c>
       <c r="I34">
-        <v>0.99999999999999556</v>
+        <v>1.0000000000000022</v>
       </c>
       <c r="J34" t="s">
         <v>47</v>
       </c>
       <c r="L34" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="M34" t="s">
         <v>46</v>
       </c>
       <c r="N34">
-        <v>1.0000000000000027</v>
+        <v>0.99999999999999956</v>
       </c>
       <c r="O34" t="s">
         <v>47</v>
@@ -2971,7 +2965,7 @@
         <v>46</v>
       </c>
       <c r="D35">
-        <v>0.99999999999999967</v>
+        <v>1.0000000000000007</v>
       </c>
       <c r="E35" t="s">
         <v>47</v>
@@ -2983,7 +2977,7 @@
         <v>46</v>
       </c>
       <c r="I35">
-        <v>0.99999999999999811</v>
+        <v>0.999999999999996</v>
       </c>
       <c r="J35" t="s">
         <v>47</v>
@@ -2997,7 +2991,7 @@
         <v>46</v>
       </c>
       <c r="D36">
-        <v>0.99999999999999878</v>
+        <v>0.99999999999999756</v>
       </c>
       <c r="E36" t="s">
         <v>47</v>
@@ -3009,7 +3003,7 @@
         <v>46</v>
       </c>
       <c r="I36">
-        <v>1.0000000000000029</v>
+        <v>1.0000000000000007</v>
       </c>
       <c r="J36" t="s">
         <v>47</v>
@@ -3023,7 +3017,7 @@
         <v>46</v>
       </c>
       <c r="D37">
-        <v>0.99999999999999989</v>
+        <v>0.99999999999999944</v>
       </c>
       <c r="E37" t="s">
         <v>47</v>
@@ -3035,7 +3029,7 @@
         <v>46</v>
       </c>
       <c r="I37">
-        <v>0.999999999999999</v>
+        <v>1.0000000000000016</v>
       </c>
       <c r="J37" t="s">
         <v>47</v>
@@ -3049,7 +3043,7 @@
         <v>46</v>
       </c>
       <c r="D38">
-        <v>0.99999999999999911</v>
+        <v>1.0000000000000004</v>
       </c>
       <c r="E38" t="s">
         <v>47</v>
@@ -3061,7 +3055,7 @@
         <v>46</v>
       </c>
       <c r="I38">
-        <v>0.99999999999999545</v>
+        <v>1.0000000000000016</v>
       </c>
       <c r="J38" t="s">
         <v>47</v>
@@ -3075,7 +3069,7 @@
         <v>46</v>
       </c>
       <c r="D39">
-        <v>0.99999999999999756</v>
+        <v>0.99999999999999956</v>
       </c>
       <c r="E39" t="s">
         <v>47</v>
@@ -3087,7 +3081,7 @@
         <v>46</v>
       </c>
       <c r="I39">
-        <v>1.0000000000000047</v>
+        <v>0.99999999999999423</v>
       </c>
       <c r="J39" t="s">
         <v>47</v>
@@ -3101,7 +3095,7 @@
         <v>46</v>
       </c>
       <c r="D40">
-        <v>1.0000000000000011</v>
+        <v>1.0000000000000009</v>
       </c>
       <c r="E40" t="s">
         <v>47</v>
@@ -3113,7 +3107,7 @@
         <v>46</v>
       </c>
       <c r="I40">
-        <v>1.0000000000000013</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="J40" t="s">
         <v>47</v>
@@ -3127,7 +3121,7 @@
         <v>46</v>
       </c>
       <c r="D41">
-        <v>0.999999999999998</v>
+        <v>1.000000000000002</v>
       </c>
       <c r="E41" t="s">
         <v>47</v>
@@ -3139,7 +3133,7 @@
         <v>46</v>
       </c>
       <c r="I41">
-        <v>0.99999999999999967</v>
+        <v>0.99999999999999944</v>
       </c>
       <c r="J41" t="s">
         <v>47</v>
@@ -3153,7 +3147,7 @@
         <v>46</v>
       </c>
       <c r="D42">
-        <v>0.999999999999999</v>
+        <v>1.0000000000000011</v>
       </c>
       <c r="E42" t="s">
         <v>47</v>
@@ -3179,7 +3173,7 @@
         <v>46</v>
       </c>
       <c r="D43">
-        <v>1.0000000000000016</v>
+        <v>0.99999999999999978</v>
       </c>
       <c r="E43" t="s">
         <v>47</v>
@@ -3191,7 +3185,7 @@
         <v>46</v>
       </c>
       <c r="I43">
-        <v>0.99999999999999845</v>
+        <v>1.0000000000000011</v>
       </c>
       <c r="J43" t="s">
         <v>47</v>
@@ -3205,7 +3199,7 @@
         <v>46</v>
       </c>
       <c r="D44">
-        <v>0.99999999999999856</v>
+        <v>0.99999999999999978</v>
       </c>
       <c r="E44" t="s">
         <v>47</v>
@@ -3217,7 +3211,7 @@
         <v>46</v>
       </c>
       <c r="I44">
-        <v>1.0000000000000042</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="J44" t="s">
         <v>47</v>
@@ -3231,7 +3225,7 @@
         <v>46</v>
       </c>
       <c r="D45">
-        <v>1.0000000000000011</v>
+        <v>0.99999999999999856</v>
       </c>
       <c r="E45" t="s">
         <v>47</v>
@@ -3243,7 +3237,7 @@
         <v>46</v>
       </c>
       <c r="I45">
-        <v>0.99999999999999634</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="J45" t="s">
         <v>47</v>
@@ -3257,7 +3251,7 @@
         <v>46</v>
       </c>
       <c r="D46">
-        <v>0.99999999999999845</v>
+        <v>1.0000000000000016</v>
       </c>
       <c r="E46" t="s">
         <v>47</v>
@@ -3269,7 +3263,7 @@
         <v>46</v>
       </c>
       <c r="I46">
-        <v>1.0000000000000011</v>
+        <v>0.99999999999999789</v>
       </c>
       <c r="J46" t="s">
         <v>47</v>
@@ -3283,7 +3277,7 @@
         <v>46</v>
       </c>
       <c r="D47">
-        <v>1.0000000000000004</v>
+        <v>0.99999999999999745</v>
       </c>
       <c r="E47" t="s">
         <v>47</v>
@@ -3295,7 +3289,7 @@
         <v>46</v>
       </c>
       <c r="I47">
-        <v>1.0000000000000013</v>
+        <v>0.99999999999999978</v>
       </c>
       <c r="J47" t="s">
         <v>47</v>
@@ -3309,7 +3303,7 @@
         <v>46</v>
       </c>
       <c r="D48">
-        <v>0.99999999999999423</v>
+        <v>1.0000000000000022</v>
       </c>
       <c r="E48" t="s">
         <v>47</v>
@@ -3321,7 +3315,7 @@
         <v>46</v>
       </c>
       <c r="I48">
-        <v>0.99999999999999767</v>
+        <v>1.0000000000000004</v>
       </c>
       <c r="J48" t="s">
         <v>47</v>
@@ -3335,7 +3329,7 @@
         <v>46</v>
       </c>
       <c r="D49">
-        <v>1.0000000000000011</v>
+        <v>1.0000000000000009</v>
       </c>
       <c r="E49" t="s">
         <v>47</v>
@@ -3347,7 +3341,7 @@
         <v>46</v>
       </c>
       <c r="I49">
-        <v>1</v>
+        <v>0.99999999999999856</v>
       </c>
       <c r="J49" t="s">
         <v>47</v>
@@ -3361,7 +3355,7 @@
         <v>46</v>
       </c>
       <c r="D50">
-        <v>0.99999999999999967</v>
+        <v>0.99999999999999989</v>
       </c>
       <c r="E50" t="s">
         <v>47</v>
@@ -3373,7 +3367,7 @@
         <v>46</v>
       </c>
       <c r="I50">
-        <v>1.0000000000000016</v>
+        <v>0.999999999999998</v>
       </c>
       <c r="J50" t="s">
         <v>47</v>
@@ -3399,7 +3393,7 @@
         <v>46</v>
       </c>
       <c r="I51">
-        <v>0.99999999999999878</v>
+        <v>1.0000000000000011</v>
       </c>
       <c r="J51" t="s">
         <v>47</v>
@@ -3413,7 +3407,7 @@
         <v>46</v>
       </c>
       <c r="D52">
-        <v>0.99999999999999856</v>
+        <v>1.0000000000000011</v>
       </c>
       <c r="E52" t="s">
         <v>47</v>
@@ -3425,7 +3419,7 @@
         <v>46</v>
       </c>
       <c r="I52">
-        <v>0.999999999999997</v>
+        <v>0.99999999999999689</v>
       </c>
       <c r="J52" t="s">
         <v>47</v>
@@ -3439,7 +3433,7 @@
         <v>46</v>
       </c>
       <c r="D53">
-        <v>0.99999999999999978</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="E53" t="s">
         <v>47</v>
@@ -3451,7 +3445,7 @@
         <v>46</v>
       </c>
       <c r="I53">
-        <v>1.0000000000000033</v>
+        <v>0.999999999999998</v>
       </c>
       <c r="J53" t="s">
         <v>47</v>
@@ -3465,7 +3459,7 @@
         <v>46</v>
       </c>
       <c r="D54">
-        <v>1.0000000000000031</v>
+        <v>1.0000000000000029</v>
       </c>
       <c r="E54" t="s">
         <v>47</v>
@@ -3477,7 +3471,7 @@
         <v>46</v>
       </c>
       <c r="I54">
-        <v>1.0000000000000029</v>
+        <v>1.0000000000000053</v>
       </c>
       <c r="J54" t="s">
         <v>47</v>
@@ -3491,7 +3485,7 @@
         <v>46</v>
       </c>
       <c r="D55">
-        <v>1.0000000000000002</v>
+        <v>1.0000000000000011</v>
       </c>
       <c r="E55" t="s">
         <v>47</v>
@@ -3503,7 +3497,7 @@
         <v>46</v>
       </c>
       <c r="I55">
-        <v>1.0000000000000018</v>
+        <v>0.99999999999999856</v>
       </c>
       <c r="J55" t="s">
         <v>47</v>
@@ -3517,7 +3511,7 @@
         <v>46</v>
       </c>
       <c r="D56">
-        <v>0.99999999999999722</v>
+        <v>0.99999999999999778</v>
       </c>
       <c r="E56" t="s">
         <v>47</v>
@@ -3529,7 +3523,7 @@
         <v>46</v>
       </c>
       <c r="I56">
-        <v>1.0000000000000004</v>
+        <v>0.99999999999999778</v>
       </c>
       <c r="J56" t="s">
         <v>47</v>
@@ -3543,7 +3537,7 @@
         <v>46</v>
       </c>
       <c r="D57">
-        <v>0.99999999999999822</v>
+        <v>0.999999999999999</v>
       </c>
       <c r="E57" t="s">
         <v>47</v>
@@ -3555,7 +3549,7 @@
         <v>46</v>
       </c>
       <c r="I57">
-        <v>1.000000000000004</v>
+        <v>1.0000000000000033</v>
       </c>
       <c r="J57" t="s">
         <v>47</v>
@@ -3569,7 +3563,7 @@
         <v>46</v>
       </c>
       <c r="D58">
-        <v>1.000000000000002</v>
+        <v>1.0000000000000011</v>
       </c>
       <c r="E58" t="s">
         <v>47</v>
@@ -3581,7 +3575,7 @@
         <v>46</v>
       </c>
       <c r="I58">
-        <v>1.0000000000000027</v>
+        <v>1</v>
       </c>
       <c r="J58" t="s">
         <v>47</v>
@@ -3595,7 +3589,7 @@
         <v>46</v>
       </c>
       <c r="D59">
-        <v>0.99999999999999678</v>
+        <v>0.99999999999999789</v>
       </c>
       <c r="E59" t="s">
         <v>47</v>
@@ -3607,7 +3601,7 @@
         <v>46</v>
       </c>
       <c r="I59">
-        <v>1.0000000000000009</v>
+        <v>1.0000000000000027</v>
       </c>
       <c r="J59" t="s">
         <v>47</v>
@@ -3621,7 +3615,7 @@
         <v>46</v>
       </c>
       <c r="D60">
-        <v>0.99999999999999634</v>
+        <v>1.0000000000000018</v>
       </c>
       <c r="E60" t="s">
         <v>47</v>
@@ -3633,7 +3627,7 @@
         <v>46</v>
       </c>
       <c r="I60">
-        <v>1.0000000000000007</v>
+        <v>1.0000000000000038</v>
       </c>
       <c r="J60" t="s">
         <v>47</v>
@@ -3647,7 +3641,7 @@
         <v>46</v>
       </c>
       <c r="D61">
-        <v>0.99999999999999878</v>
+        <v>1.0000000000000016</v>
       </c>
       <c r="E61" t="s">
         <v>47</v>
@@ -3659,7 +3653,7 @@
         <v>46</v>
       </c>
       <c r="I61">
-        <v>1.0000000000000029</v>
+        <v>0.99999999999999822</v>
       </c>
       <c r="J61" t="s">
         <v>47</v>
@@ -3673,7 +3667,7 @@
         <v>46</v>
       </c>
       <c r="D62">
-        <v>1.0000000000000007</v>
+        <v>0.99999999999999967</v>
       </c>
       <c r="E62" t="s">
         <v>47</v>
@@ -3685,7 +3679,7 @@
         <v>46</v>
       </c>
       <c r="I62">
-        <v>1.0000000000000027</v>
+        <v>0.99999999999999789</v>
       </c>
       <c r="J62" t="s">
         <v>47</v>
@@ -3699,7 +3693,7 @@
         <v>46</v>
       </c>
       <c r="D63">
-        <v>1.0000000000000031</v>
+        <v>0.99999999999999722</v>
       </c>
       <c r="E63" t="s">
         <v>47</v>
@@ -3711,7 +3705,7 @@
         <v>46</v>
       </c>
       <c r="I63">
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="J63" t="s">
         <v>47</v>
@@ -3725,7 +3719,7 @@
         <v>46</v>
       </c>
       <c r="D64">
-        <v>0.99999999999999656</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="E64" t="s">
         <v>47</v>
@@ -3737,7 +3731,7 @@
         <v>46</v>
       </c>
       <c r="I64">
-        <v>1.0000000000000013</v>
+        <v>0.99999999999999589</v>
       </c>
       <c r="J64" t="s">
         <v>47</v>
@@ -3751,7 +3745,7 @@
         <v>46</v>
       </c>
       <c r="D65">
-        <v>1.0000000000000022</v>
+        <v>0.99999999999999922</v>
       </c>
       <c r="E65" t="s">
         <v>47</v>
@@ -3763,7 +3757,7 @@
         <v>46</v>
       </c>
       <c r="I65">
-        <v>1.0000000000000042</v>
+        <v>0.99999999999999534</v>
       </c>
       <c r="J65" t="s">
         <v>47</v>
@@ -3777,7 +3771,7 @@
         <v>46</v>
       </c>
       <c r="D66">
-        <v>0.99999999999999911</v>
+        <v>1.0000000000000011</v>
       </c>
       <c r="E66" t="s">
         <v>47</v>
@@ -3789,7 +3783,7 @@
         <v>46</v>
       </c>
       <c r="I66">
-        <v>1.0000000000000024</v>
+        <v>1.0000000000000007</v>
       </c>
       <c r="J66" t="s">
         <v>47</v>
@@ -3803,7 +3797,7 @@
         <v>46</v>
       </c>
       <c r="D67">
-        <v>0.99999999999999811</v>
+        <v>1.0000000000000022</v>
       </c>
       <c r="E67" t="s">
         <v>47</v>
@@ -3815,7 +3809,7 @@
         <v>46</v>
       </c>
       <c r="I67">
-        <v>0.99999999999999711</v>
+        <v>0.99999999999999956</v>
       </c>
       <c r="J67" t="s">
         <v>47</v>
@@ -3829,7 +3823,7 @@
         <v>46</v>
       </c>
       <c r="D68">
-        <v>1</v>
+        <v>0.99999999999999956</v>
       </c>
       <c r="E68" t="s">
         <v>47</v>
@@ -3841,7 +3835,7 @@
         <v>46</v>
       </c>
       <c r="I68">
-        <v>0.99999999999999756</v>
+        <v>1.0000000000000016</v>
       </c>
       <c r="J68" t="s">
         <v>47</v>
@@ -3855,7 +3849,7 @@
         <v>46</v>
       </c>
       <c r="D69">
-        <v>1.0000000000000016</v>
+        <v>0.99999999999999822</v>
       </c>
       <c r="E69" t="s">
         <v>47</v>
@@ -3867,7 +3861,7 @@
         <v>46</v>
       </c>
       <c r="I69">
-        <v>0.99999999999999856</v>
+        <v>0.99999999999999589</v>
       </c>
       <c r="J69" t="s">
         <v>47</v>
@@ -3881,7 +3875,7 @@
         <v>46</v>
       </c>
       <c r="D70">
-        <v>1.0000000000000004</v>
+        <v>1.0000000000000018</v>
       </c>
       <c r="E70" t="s">
         <v>47</v>
@@ -3893,7 +3887,7 @@
         <v>46</v>
       </c>
       <c r="I70">
-        <v>0.99999999999999689</v>
+        <v>0.99999999999999845</v>
       </c>
       <c r="J70" t="s">
         <v>47</v>
@@ -3907,7 +3901,7 @@
         <v>46</v>
       </c>
       <c r="D71">
-        <v>0.99999999999999944</v>
+        <v>0.99999999999999967</v>
       </c>
       <c r="E71" t="s">
         <v>47</v>
@@ -3919,7 +3913,7 @@
         <v>46</v>
       </c>
       <c r="I71">
-        <v>1</v>
+        <v>1.0000000000000004</v>
       </c>
       <c r="J71" t="s">
         <v>47</v>
@@ -3933,7 +3927,7 @@
         <v>46</v>
       </c>
       <c r="D72">
-        <v>1.0000000000000018</v>
+        <v>1.0000000000000027</v>
       </c>
       <c r="E72" t="s">
         <v>47</v>
@@ -3945,7 +3939,7 @@
         <v>46</v>
       </c>
       <c r="I72">
-        <v>0.99999999999999756</v>
+        <v>1.0000000000000033</v>
       </c>
       <c r="J72" t="s">
         <v>47</v>
@@ -3959,7 +3953,7 @@
         <v>46</v>
       </c>
       <c r="D73">
-        <v>0.99999999999999889</v>
+        <v>1.0000000000000016</v>
       </c>
       <c r="E73" t="s">
         <v>47</v>
@@ -3971,7 +3965,7 @@
         <v>46</v>
       </c>
       <c r="I73">
-        <v>0.99999999999999356</v>
+        <v>0.99999999999999856</v>
       </c>
       <c r="J73" t="s">
         <v>47</v>
@@ -3985,7 +3979,7 @@
         <v>46</v>
       </c>
       <c r="D74">
-        <v>0.99999999999999911</v>
+        <v>1</v>
       </c>
       <c r="E74" t="s">
         <v>47</v>
@@ -4011,7 +4005,7 @@
         <v>46</v>
       </c>
       <c r="D75">
-        <v>1.0000000000000027</v>
+        <v>0.99999999999999856</v>
       </c>
       <c r="E75" t="s">
         <v>47</v>
@@ -4023,7 +4017,7 @@
         <v>46</v>
       </c>
       <c r="I75">
-        <v>1.0000000000000013</v>
+        <v>0.99999999999999778</v>
       </c>
       <c r="J75" t="s">
         <v>47</v>
@@ -4037,7 +4031,7 @@
         <v>46</v>
       </c>
       <c r="D76">
-        <v>1</v>
+        <v>0.99999999999999933</v>
       </c>
       <c r="E76" t="s">
         <v>47</v>
@@ -4049,7 +4043,7 @@
         <v>46</v>
       </c>
       <c r="I76">
-        <v>1.0000000000000018</v>
+        <v>1.0000000000000004</v>
       </c>
       <c r="J76" t="s">
         <v>47</v>
@@ -4063,21 +4057,9 @@
         <v>46</v>
       </c>
       <c r="D77">
-        <v>0.99999999999999756</v>
+        <v>1.0000000000000016</v>
       </c>
       <c r="E77" t="s">
-        <v>47</v>
-      </c>
-      <c r="G77" t="s">
-        <v>191</v>
-      </c>
-      <c r="H77" t="s">
-        <v>46</v>
-      </c>
-      <c r="I77">
-        <v>0.99999999999999989</v>
-      </c>
-      <c r="J77" t="s">
         <v>47</v>
       </c>
     </row>
@@ -4089,7 +4071,7 @@
         <v>46</v>
       </c>
       <c r="D78">
-        <v>1.0000000000000036</v>
+        <v>1.0000000000000007</v>
       </c>
       <c r="E78" t="s">
         <v>47</v>
@@ -4103,7 +4085,7 @@
         <v>46</v>
       </c>
       <c r="D79">
-        <v>0.99999999999999789</v>
+        <v>1.0000000000000013</v>
       </c>
       <c r="E79" t="s">
         <v>47</v>
@@ -4117,7 +4099,7 @@
         <v>46</v>
       </c>
       <c r="D80">
-        <v>1.0000000000000013</v>
+        <v>0.99999999999999867</v>
       </c>
       <c r="E80" t="s">
         <v>47</v>
@@ -4131,7 +4113,7 @@
         <v>46</v>
       </c>
       <c r="D81">
-        <v>1.0000000000000024</v>
+        <v>0.99999999999999956</v>
       </c>
       <c r="E81" t="s">
         <v>47</v>
@@ -4145,7 +4127,7 @@
         <v>46</v>
       </c>
       <c r="D82">
-        <v>1.0000000000000011</v>
+        <v>1.0000000000000022</v>
       </c>
       <c r="E82" t="s">
         <v>47</v>
@@ -4159,7 +4141,7 @@
         <v>46</v>
       </c>
       <c r="D83">
-        <v>0.99999999999999933</v>
+        <v>1.0000000000000027</v>
       </c>
       <c r="E83" t="s">
         <v>47</v>
@@ -4173,7 +4155,7 @@
         <v>46</v>
       </c>
       <c r="D84">
-        <v>0.99999999999999889</v>
+        <v>1.0000000000000007</v>
       </c>
       <c r="E84" t="s">
         <v>47</v>
@@ -4187,7 +4169,7 @@
         <v>46</v>
       </c>
       <c r="D85">
-        <v>0.99999999999999889</v>
+        <v>1.0000000000000016</v>
       </c>
       <c r="E85" t="s">
         <v>47</v>
@@ -4201,7 +4183,7 @@
         <v>46</v>
       </c>
       <c r="D86">
-        <v>0.99999999999999856</v>
+        <v>0.99999999999999967</v>
       </c>
       <c r="E86" t="s">
         <v>47</v>
@@ -4215,7 +4197,7 @@
         <v>46</v>
       </c>
       <c r="D87">
-        <v>0.99999999999999689</v>
+        <v>0.99999999999999967</v>
       </c>
       <c r="E87" t="s">
         <v>47</v>
@@ -4229,7 +4211,7 @@
         <v>46</v>
       </c>
       <c r="D88">
-        <v>0.99999999999999833</v>
+        <v>0.99999999999999634</v>
       </c>
       <c r="E88" t="s">
         <v>47</v>
@@ -4241,8 +4223,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90122CEF-754C-4C04-97A4-74AECC8987C3}">
-  <dimension ref="B9:T179"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FB276FB-00F3-440B-A84E-80AD8F8D3729}">
+  <dimension ref="B9:T178"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="9" spans="2:20" x14ac:dyDescent="0.25">
@@ -4308,4965 +4290,4936 @@
         <v>41</v>
       </c>
       <c r="S10" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="T10" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="11" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C11" t="s">
         <v>31</v>
       </c>
       <c r="D11">
-        <v>0.54949346191534365</v>
+        <v>0.5917200611898038</v>
       </c>
       <c r="F11" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G11" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H11">
-        <v>0.16141018449171288</v>
+        <v>0.22466576925398296</v>
       </c>
       <c r="J11" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="K11" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="L11">
-        <v>0.16377766541100416</v>
+        <v>0.15478887184711895</v>
       </c>
       <c r="N11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="O11">
-        <v>0.22632325847364129</v>
+        <v>0.14921455054256713</v>
       </c>
       <c r="Q11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="R11" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S11" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T11">
-        <v>0.22632325847364129</v>
+        <v>0.14921455054256713</v>
       </c>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C12" t="s">
         <v>31</v>
       </c>
       <c r="D12">
-        <v>0.54038007316950631</v>
+        <v>0.5900249966232769</v>
       </c>
       <c r="F12" t="s">
+        <v>385</v>
+      </c>
+      <c r="G12" t="s">
+        <v>384</v>
+      </c>
+      <c r="H12">
+        <v>6.2212463568192076E-3</v>
+      </c>
+      <c r="J12" t="s">
+        <v>385</v>
+      </c>
+      <c r="K12" t="s">
         <v>387</v>
       </c>
-      <c r="G12" t="s">
-        <v>386</v>
-      </c>
-      <c r="H12">
-        <v>6.0508846876677815E-3</v>
-      </c>
-      <c r="J12" t="s">
-        <v>387</v>
-      </c>
-      <c r="K12" t="s">
-        <v>389</v>
-      </c>
       <c r="L12">
-        <v>1.191401751674538E-2</v>
+        <v>1.1617939153150124E-2</v>
       </c>
       <c r="N12" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="O12">
-        <v>0.23608463582779191</v>
+        <v>0.15499224609438633</v>
       </c>
       <c r="Q12" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="R12" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S12" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T12">
-        <v>0.23608463582779191</v>
+        <v>0.15499224609438633</v>
       </c>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C13" t="s">
         <v>31</v>
       </c>
       <c r="D13">
-        <v>0.54996722585002356</v>
+        <v>0.58875230580246729</v>
       </c>
       <c r="F13" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G13" t="s">
+        <v>384</v>
+      </c>
+      <c r="H13">
+        <v>7.1808940716054843E-4</v>
+      </c>
+      <c r="J13" t="s">
         <v>386</v>
       </c>
-      <c r="H13">
-        <v>7.4410386624915495E-4</v>
-      </c>
-      <c r="J13" t="s">
-        <v>388</v>
-      </c>
       <c r="K13" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="L13">
-        <v>2.3766961147039622E-3</v>
+        <v>2.5571304330672573E-3</v>
       </c>
       <c r="N13" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O13">
-        <v>0.22398396896624118</v>
+        <v>0.1543259741570856</v>
       </c>
       <c r="Q13" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R13" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S13" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T13">
-        <v>0.22398396896624118</v>
+        <v>0.1543259741570856</v>
       </c>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C14" t="s">
         <v>31</v>
       </c>
       <c r="D14">
-        <v>0.55388734347671098</v>
+        <v>0.58468553043824556</v>
       </c>
       <c r="N14" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O14">
-        <v>0.22071385243482186</v>
+        <v>0.14796515175115071</v>
       </c>
       <c r="Q14" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="R14" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S14" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T14">
-        <v>0.22071385243482186</v>
+        <v>0.14796515175115071</v>
       </c>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C15" t="s">
         <v>31</v>
       </c>
       <c r="D15">
-        <v>0.55716814300905748</v>
+        <v>0.58781002872451527</v>
       </c>
       <c r="N15" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O15">
-        <v>0.21808257265479988</v>
+        <v>0.15630467505447165</v>
       </c>
       <c r="Q15" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="R15" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S15" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T15">
-        <v>0.21808257265479988</v>
+        <v>0.15630467505447165</v>
       </c>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C16" t="s">
         <v>31</v>
       </c>
       <c r="D16">
-        <v>0.5711442839980142</v>
+        <v>0.58684100062003375</v>
       </c>
       <c r="N16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="O16">
-        <v>0.20716984292863727</v>
+        <v>0.15468464233927334</v>
       </c>
       <c r="Q16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="R16" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S16" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T16">
-        <v>0.20716984292863727</v>
+        <v>0.15468464233927334</v>
       </c>
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C17" t="s">
         <v>31</v>
       </c>
       <c r="D17">
-        <v>0.56542576483501694</v>
+        <v>0.59333707830816984</v>
       </c>
       <c r="N17" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O17">
-        <v>0.20924147287681061</v>
+        <v>0.16272239005969921</v>
       </c>
       <c r="Q17" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="R17" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S17" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T17">
-        <v>0.20924147287681061</v>
+        <v>0.16272239005969921</v>
       </c>
     </row>
     <row r="18" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C18" t="s">
         <v>31</v>
       </c>
       <c r="D18">
-        <v>0.56679634088019659</v>
+        <v>0.59006807408853901</v>
       </c>
       <c r="N18" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="O18">
-        <v>0.20430145058458152</v>
+        <v>0.15842976699188863</v>
       </c>
       <c r="Q18" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="R18" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S18" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T18">
-        <v>0.20430145058458152</v>
+        <v>0.15842976699188863</v>
       </c>
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C19" t="s">
         <v>31</v>
       </c>
       <c r="D19">
-        <v>0.56395728213714214</v>
+        <v>0.5849105174777729</v>
       </c>
       <c r="N19" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="O19">
-        <v>0.20774509551843251</v>
+        <v>0.15608418660053927</v>
       </c>
       <c r="Q19" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="R19" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S19" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T19">
-        <v>0.20774509551843251</v>
+        <v>0.15608418660053927</v>
       </c>
     </row>
     <row r="20" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C20" t="s">
         <v>31</v>
       </c>
       <c r="D20">
-        <v>0.56567937618811404</v>
+        <v>0.58572854367544391</v>
       </c>
       <c r="N20" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O20">
-        <v>0.21018545645312081</v>
+        <v>0.15787435991835091</v>
       </c>
       <c r="Q20" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="R20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S20" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T20">
-        <v>0.21018545645312081</v>
+        <v>0.15787435991835091</v>
       </c>
     </row>
     <row r="21" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C21" t="s">
         <v>31</v>
       </c>
       <c r="D21">
-        <v>0.56315669114929567</v>
+        <v>0.59035817491691689</v>
       </c>
       <c r="N21" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O21">
-        <v>0.20906513416656805</v>
+        <v>0.15889494161908382</v>
       </c>
       <c r="Q21" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="R21" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S21" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T21">
-        <v>0.20906513416656805</v>
+        <v>0.15889494161908382</v>
       </c>
     </row>
     <row r="22" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C22" t="s">
         <v>31</v>
       </c>
       <c r="D22">
-        <v>0.53100467286591024</v>
+        <v>0.58563905625633506</v>
       </c>
       <c r="N22" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="O22">
-        <v>0.23898222219536738</v>
+        <v>0.16071131939186567</v>
       </c>
       <c r="Q22" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="R22" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S22" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T22">
-        <v>0.23898222219536738</v>
+        <v>0.16071131939186567</v>
       </c>
     </row>
     <row r="23" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C23" t="s">
         <v>31</v>
       </c>
       <c r="D23">
-        <v>0.53574805662952352</v>
+        <v>0.58922103698382888</v>
       </c>
       <c r="N23" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O23">
-        <v>0.22555065629187859</v>
+        <v>0.17416133967719716</v>
       </c>
       <c r="Q23" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="R23" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S23" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T23">
-        <v>0.22555065629187859</v>
+        <v>0.17416133967719716</v>
       </c>
     </row>
     <row r="24" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C24" t="s">
         <v>31</v>
       </c>
       <c r="D24">
-        <v>0.53060483193732444</v>
+        <v>0.58520282507265253</v>
       </c>
       <c r="N24" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="O24">
-        <v>0.24697144731534071</v>
+        <v>0.17370596339121541</v>
       </c>
       <c r="Q24" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="R24" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S24" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T24">
-        <v>0.24697144731534071</v>
+        <v>0.17370596339121541</v>
       </c>
     </row>
     <row r="25" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C25" t="s">
         <v>31</v>
       </c>
       <c r="D25">
-        <v>0.53355978685867267</v>
+        <v>0.58359570967974839</v>
       </c>
       <c r="N25" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="O25">
-        <v>0.23533559479009</v>
+        <v>0.17814673525277924</v>
       </c>
       <c r="Q25" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="R25" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S25" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T25">
-        <v>0.23533559479009</v>
+        <v>0.17814673525277924</v>
       </c>
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C26" t="s">
         <v>31</v>
       </c>
       <c r="D26">
-        <v>0.54004757030543349</v>
+        <v>0.58258430990434273</v>
       </c>
       <c r="N26" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O26">
-        <v>0.21896777063441222</v>
+        <v>0.1771698143064481</v>
       </c>
       <c r="Q26" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="R26" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S26" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T26">
-        <v>0.21896777063441222</v>
+        <v>0.1771698143064481</v>
       </c>
     </row>
     <row r="27" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C27" t="s">
         <v>31</v>
       </c>
       <c r="D27">
-        <v>0.53902411664150252</v>
+        <v>0.5829067278543637</v>
       </c>
       <c r="N27" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O27">
-        <v>0.22206748540624693</v>
+        <v>0.17235841110581962</v>
       </c>
       <c r="Q27" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="R27" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S27" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T27">
-        <v>0.22206748540624693</v>
+        <v>0.17235841110581962</v>
       </c>
     </row>
     <row r="28" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C28" t="s">
         <v>31</v>
       </c>
       <c r="D28">
-        <v>0.55228986569597738</v>
+        <v>0.5838883049297332</v>
       </c>
       <c r="N28" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="O28">
-        <v>0.217304927385331</v>
+        <v>0.17633233896502121</v>
       </c>
       <c r="Q28" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="R28" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S28" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T28">
-        <v>0.217304927385331</v>
+        <v>0.17633233896502121</v>
       </c>
     </row>
     <row r="29" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C29" t="s">
         <v>31</v>
       </c>
       <c r="D29">
-        <v>0.55117301916063233</v>
+        <v>0.58901022627919852</v>
       </c>
       <c r="N29" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="O29">
-        <v>0.21521180768067663</v>
+        <v>0.16301538932034407</v>
       </c>
       <c r="Q29" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R29" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S29" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T29">
-        <v>0.21521180768067663</v>
+        <v>0.16301538932034407</v>
       </c>
     </row>
     <row r="30" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C30" t="s">
         <v>31</v>
       </c>
       <c r="D30">
-        <v>0.54287105023866844</v>
+        <v>0.58770114158171893</v>
       </c>
       <c r="N30" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O30">
-        <v>0.22017903385001619</v>
+        <v>0.16591084951150276</v>
       </c>
       <c r="Q30" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="R30" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S30" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T30">
-        <v>0.22017903385001619</v>
+        <v>0.16591084951150276</v>
       </c>
     </row>
     <row r="31" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C31" t="s">
         <v>31</v>
       </c>
       <c r="D31">
-        <v>0.54403502463605691</v>
+        <v>0.58941473945423883</v>
       </c>
       <c r="N31" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O31">
-        <v>0.2254151415854431</v>
+        <v>0.16640384137024217</v>
       </c>
       <c r="Q31" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="R31" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S31" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T31">
-        <v>0.2254151415854431</v>
+        <v>0.16640384137024217</v>
       </c>
     </row>
     <row r="32" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C32" t="s">
         <v>31</v>
       </c>
       <c r="D32">
-        <v>0.54116084343359183</v>
+        <v>0.58776901893031397</v>
       </c>
       <c r="N32" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O32">
-        <v>0.2235328051702338</v>
+        <v>0.16865057835013361</v>
       </c>
       <c r="Q32" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="R32" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S32" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T32">
-        <v>0.2235328051702338</v>
+        <v>0.16865057835013361</v>
       </c>
     </row>
     <row r="33" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C33" t="s">
         <v>31</v>
       </c>
       <c r="D33">
-        <v>0.55031967766462653</v>
+        <v>0.58485723072069784</v>
       </c>
       <c r="N33" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O33">
-        <v>0.21401516885375729</v>
+        <v>0.16279617898620558</v>
       </c>
       <c r="Q33" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="R33" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S33" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T33">
-        <v>0.21401516885375729</v>
+        <v>0.16279617898620558</v>
       </c>
     </row>
     <row r="34" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C34" t="s">
         <v>31</v>
       </c>
       <c r="D34">
-        <v>0.54276699141567541</v>
+        <v>0.58611099151301205</v>
       </c>
       <c r="N34" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O34">
-        <v>0.21807494920671319</v>
+        <v>0.16573497465511697</v>
       </c>
       <c r="Q34" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="R34" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S34" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T34">
-        <v>0.21807494920671319</v>
+        <v>0.16573497465511697</v>
       </c>
     </row>
     <row r="35" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C35" t="s">
         <v>31</v>
       </c>
       <c r="D35">
-        <v>0.54615681868113453</v>
+        <v>0.58432461123420087</v>
       </c>
       <c r="N35" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O35">
-        <v>0.21001904644785074</v>
+        <v>0.1663499013493441</v>
       </c>
       <c r="Q35" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="R35" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S35" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T35">
-        <v>0.21001904644785074</v>
+        <v>0.1663499013493441</v>
       </c>
     </row>
     <row r="36" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C36" t="s">
         <v>31</v>
       </c>
       <c r="D36">
-        <v>0.5432461727128044</v>
+        <v>0.58770053231478392</v>
       </c>
       <c r="N36" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O36">
-        <v>0.21542438929202043</v>
+        <v>0.16385645511044528</v>
       </c>
       <c r="Q36" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="R36" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S36" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T36">
-        <v>0.21542438929202043</v>
+        <v>0.16385645511044528</v>
       </c>
     </row>
     <row r="37" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C37" t="s">
         <v>31</v>
       </c>
       <c r="D37">
-        <v>0.54253610071402936</v>
+        <v>0.58851790855433384</v>
       </c>
       <c r="N37" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="O37">
-        <v>0.21934015231555645</v>
+        <v>0.16829939764244675</v>
       </c>
       <c r="Q37" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="R37" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S37" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T37">
-        <v>0.21934015231555645</v>
+        <v>0.16829939764244675</v>
       </c>
     </row>
     <row r="38" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C38" t="s">
         <v>31</v>
       </c>
       <c r="D38">
-        <v>0.54313600288778585</v>
+        <v>0.58494852650858542</v>
       </c>
       <c r="N38" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O38">
-        <v>0.21803583402231838</v>
+        <v>0.17323245461889122</v>
       </c>
       <c r="Q38" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="R38" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S38" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T38">
-        <v>0.21803583402231838</v>
+        <v>0.17323245461889122</v>
       </c>
     </row>
     <row r="39" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C39" t="s">
         <v>31</v>
       </c>
       <c r="D39">
-        <v>0.52983145635897844</v>
+        <v>0.57937384722086527</v>
       </c>
       <c r="N39" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="O39">
-        <v>0.24888573822740181</v>
+        <v>0.17345160059201101</v>
       </c>
       <c r="Q39" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="R39" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S39" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T39">
-        <v>0.24888573822740181</v>
+        <v>0.17345160059201101</v>
       </c>
     </row>
     <row r="40" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C40" t="s">
         <v>31</v>
       </c>
       <c r="D40">
-        <v>0.53748854096215515</v>
+        <v>0.58208969290214074</v>
       </c>
       <c r="N40" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="O40">
-        <v>0.23637435224349601</v>
+        <v>0.17093148798575211</v>
       </c>
       <c r="Q40" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="R40" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S40" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T40">
-        <v>0.23637435224349601</v>
+        <v>0.17093148798575211</v>
       </c>
     </row>
     <row r="41" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C41" t="s">
         <v>31</v>
       </c>
       <c r="D41">
-        <v>0.54757539461291294</v>
+        <v>0.5842995701004351</v>
       </c>
       <c r="N41" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="O41">
-        <v>0.22577286873040309</v>
+        <v>0.16652343691758006</v>
       </c>
       <c r="Q41" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="R41" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S41" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T41">
-        <v>0.22577286873040309</v>
+        <v>0.16652343691758006</v>
       </c>
     </row>
     <row r="42" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C42" t="s">
         <v>31</v>
       </c>
       <c r="D42">
-        <v>0.55609682819228179</v>
+        <v>0.5792437444878844</v>
       </c>
       <c r="N42" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O42">
-        <v>0.19888113483365949</v>
+        <v>0.17494280153417074</v>
       </c>
       <c r="Q42" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="R42" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S42" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T42">
-        <v>0.19888113483365949</v>
+        <v>0.17494280153417074</v>
       </c>
     </row>
     <row r="43" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C43" t="s">
         <v>31</v>
       </c>
       <c r="D43">
-        <v>0.55284347066346118</v>
+        <v>0.58897855452572911</v>
       </c>
       <c r="N43" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O43">
-        <v>0.19674783911085533</v>
+        <v>0.16614548140167795</v>
       </c>
       <c r="Q43" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="R43" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S43" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T43">
-        <v>0.19674783911085533</v>
+        <v>0.16614548140167795</v>
       </c>
     </row>
     <row r="44" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C44" t="s">
         <v>31</v>
       </c>
       <c r="D44">
-        <v>0.55278087578343005</v>
+        <v>0.58702063061034604</v>
       </c>
       <c r="N44" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="O44">
-        <v>0.20183555688987137</v>
+        <v>0.16561473375834387</v>
       </c>
       <c r="Q44" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="R44" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S44" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T44">
-        <v>0.20183555688987137</v>
+        <v>0.16561473375834387</v>
       </c>
     </row>
     <row r="45" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C45" t="s">
         <v>31</v>
       </c>
       <c r="D45">
-        <v>0.55491439603527049</v>
+        <v>0.58417701132309618</v>
       </c>
       <c r="N45" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="O45">
-        <v>0.20250366197158398</v>
+        <v>0.17063785288463323</v>
       </c>
       <c r="Q45" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="R45" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S45" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T45">
-        <v>0.20250366197158398</v>
+        <v>0.17063785288463323</v>
       </c>
     </row>
     <row r="46" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C46" t="s">
         <v>31</v>
       </c>
       <c r="D46">
-        <v>0.55361938449114223</v>
+        <v>0.58286153826835385</v>
       </c>
       <c r="N46" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O46">
-        <v>0.19399898879293612</v>
+        <v>0.16975335059086782</v>
       </c>
       <c r="Q46" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="R46" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S46" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T46">
-        <v>0.19399898879293612</v>
+        <v>0.16975335059086782</v>
       </c>
     </row>
     <row r="47" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C47" t="s">
         <v>31</v>
       </c>
       <c r="D47">
-        <v>0.55203180562499099</v>
+        <v>0.58196336676329186</v>
       </c>
       <c r="N47" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="O47">
-        <v>0.19002616058542005</v>
+        <v>0.17056797778372162</v>
       </c>
       <c r="Q47" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="R47" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S47" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T47">
-        <v>0.19002616058542005</v>
+        <v>0.17056797778372162</v>
       </c>
     </row>
     <row r="48" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C48" t="s">
         <v>31</v>
       </c>
       <c r="D48">
-        <v>0.5528516489244083</v>
+        <v>0.58341409033762059</v>
       </c>
       <c r="N48" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="O48">
-        <v>0.19081899351568599</v>
+        <v>0.16857619893876616</v>
       </c>
       <c r="Q48" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="R48" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S48" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T48">
-        <v>0.19081899351568599</v>
+        <v>0.16857619893876616</v>
       </c>
     </row>
     <row r="49" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C49" t="s">
         <v>31</v>
       </c>
       <c r="D49">
-        <v>0.56721905321430854</v>
+        <v>0.58037867175037783</v>
       </c>
       <c r="N49" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O49">
-        <v>0.19596525251450719</v>
+        <v>0.17392726710913886</v>
       </c>
       <c r="Q49" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="R49" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S49" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T49">
-        <v>0.19596525251450719</v>
+        <v>0.17392726710913886</v>
       </c>
     </row>
     <row r="50" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C50" t="s">
         <v>31</v>
       </c>
       <c r="D50">
-        <v>0.56128046416751187</v>
+        <v>0.58941449631877674</v>
       </c>
       <c r="N50" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O50">
-        <v>0.19005476699794033</v>
+        <v>0.17271558916059351</v>
       </c>
       <c r="Q50" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="R50" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S50" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T50">
-        <v>0.19005476699794033</v>
+        <v>0.17271558916059351</v>
       </c>
     </row>
     <row r="51" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C51" t="s">
         <v>31</v>
       </c>
       <c r="D51">
-        <v>0.54938567560101492</v>
+        <v>0.59327879535009853</v>
       </c>
       <c r="N51" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O51">
-        <v>0.18570453114884938</v>
+        <v>0.171404868100657</v>
       </c>
       <c r="Q51" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="R51" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S51" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T51">
-        <v>0.18570453114884938</v>
+        <v>0.171404868100657</v>
       </c>
     </row>
     <row r="52" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C52" t="s">
         <v>31</v>
       </c>
       <c r="D52">
-        <v>0.5539028346405046</v>
+        <v>0.58822918415141412</v>
       </c>
       <c r="N52" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O52">
-        <v>0.18859079307577328</v>
+        <v>0.16880118243674597</v>
       </c>
       <c r="Q52" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="R52" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S52" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T52">
-        <v>0.18859079307577328</v>
+        <v>0.16880118243674597</v>
       </c>
     </row>
     <row r="53" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C53" t="s">
         <v>31</v>
       </c>
       <c r="D53">
-        <v>0.5597653955611096</v>
+        <v>0.58574272566794583</v>
       </c>
       <c r="N53" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O53">
-        <v>0.18248603156951565</v>
+        <v>0.17268760489247781</v>
       </c>
       <c r="Q53" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="R53" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S53" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T53">
-        <v>0.18248603156951565</v>
+        <v>0.17268760489247781</v>
       </c>
     </row>
     <row r="54" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C54" t="s">
         <v>31</v>
       </c>
       <c r="D54">
-        <v>0.55539548665362637</v>
+        <v>0.59041653297973928</v>
       </c>
       <c r="N54" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="O54">
-        <v>0.18863556744571675</v>
+        <v>0.16998608721947558</v>
       </c>
       <c r="Q54" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="R54" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S54" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T54">
-        <v>0.18863556744571675</v>
+        <v>0.16998608721947558</v>
       </c>
     </row>
     <row r="55" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C55" t="s">
         <v>31</v>
       </c>
       <c r="D55">
-        <v>0.56085086144251139</v>
+        <v>0.58436524790839661</v>
       </c>
       <c r="N55" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="O55">
-        <v>0.18226644116699489</v>
+        <v>0.17338723134643946</v>
       </c>
       <c r="Q55" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="R55" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S55" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T55">
-        <v>0.18226644116699489</v>
+        <v>0.17338723134643946</v>
       </c>
     </row>
     <row r="56" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C56" t="s">
         <v>31</v>
       </c>
       <c r="D56">
-        <v>0.55303545728286585</v>
+        <v>0.58173780005328968</v>
       </c>
       <c r="N56" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O56">
-        <v>0.18362388282277595</v>
+        <v>0.17583122238373228</v>
       </c>
       <c r="Q56" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="R56" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S56" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T56">
-        <v>0.18362388282277595</v>
+        <v>0.17583122238373228</v>
       </c>
     </row>
     <row r="57" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C57" t="s">
         <v>31</v>
       </c>
       <c r="D57">
-        <v>0.55493263054277797</v>
+        <v>0.58898481923082846</v>
       </c>
       <c r="N57" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O57">
-        <v>0.2016320531867834</v>
+        <v>0.16739326644074345</v>
       </c>
       <c r="Q57" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="R57" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S57" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T57">
-        <v>0.2016320531867834</v>
+        <v>0.16739326644074345</v>
       </c>
     </row>
     <row r="58" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C58" t="s">
         <v>31</v>
       </c>
       <c r="D58">
-        <v>0.55572170583371805</v>
+        <v>0.59521747685643556</v>
       </c>
       <c r="N58" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O58">
-        <v>0.19670690026308052</v>
+        <v>0.16660187203186527</v>
       </c>
       <c r="Q58" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="R58" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S58" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T58">
-        <v>0.19670690026308052</v>
+        <v>0.16660187203186527</v>
       </c>
     </row>
     <row r="59" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C59" t="s">
         <v>31</v>
       </c>
       <c r="D59">
-        <v>0.56418308265332862</v>
+        <v>0.59093619603168523</v>
       </c>
       <c r="N59" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="O59">
-        <v>0.19865958538818318</v>
+        <v>0.16974506505223458</v>
       </c>
       <c r="Q59" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="R59" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S59" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T59">
-        <v>0.19865958538818318</v>
+        <v>0.16974506505223458</v>
       </c>
     </row>
     <row r="60" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C60" t="s">
         <v>31</v>
       </c>
       <c r="D60">
-        <v>0.56760590044930459</v>
+        <v>0.59147147688206858</v>
       </c>
       <c r="N60" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O60">
-        <v>0.19616829043285142</v>
+        <v>0.16648026424319037</v>
       </c>
       <c r="Q60" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="R60" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S60" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T60">
-        <v>0.19616829043285142</v>
+        <v>0.16648026424319037</v>
       </c>
     </row>
     <row r="61" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C61" t="s">
         <v>31</v>
       </c>
       <c r="D61">
-        <v>0.56411388093520787</v>
+        <v>0.59871684906144151</v>
       </c>
       <c r="N61" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="O61">
-        <v>0.19935430782037877</v>
+        <v>0.16139987859983942</v>
       </c>
       <c r="Q61" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="R61" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S61" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T61">
-        <v>0.19935430782037877</v>
+        <v>0.16139987859983942</v>
       </c>
     </row>
     <row r="62" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C62" t="s">
         <v>31</v>
       </c>
       <c r="D62">
-        <v>0.55641814367246334</v>
+        <v>0.59890649329232948</v>
       </c>
       <c r="N62" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="O62">
-        <v>0.20755653004072117</v>
+        <v>0.16118527391319687</v>
       </c>
       <c r="Q62" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="R62" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S62" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T62">
-        <v>0.20755653004072117</v>
+        <v>0.16118527391319687</v>
       </c>
     </row>
     <row r="63" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C63" t="s">
         <v>31</v>
       </c>
       <c r="D63">
-        <v>0.56639596106765244</v>
+        <v>0.59438950411826785</v>
       </c>
       <c r="N63" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O63">
-        <v>0.20095422420724687</v>
+        <v>0.16443395309586051</v>
       </c>
       <c r="Q63" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="R63" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S63" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T63">
-        <v>0.20095422420724687</v>
+        <v>0.16443395309586051</v>
       </c>
     </row>
     <row r="64" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C64" t="s">
         <v>31</v>
       </c>
       <c r="D64">
-        <v>0.55901650540741521</v>
+        <v>0.58898381403350564</v>
       </c>
       <c r="N64" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="O64">
-        <v>0.20396845178565201</v>
+        <v>0.16623910496633323</v>
       </c>
       <c r="Q64" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="R64" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S64" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T64">
-        <v>0.20396845178565201</v>
+        <v>0.16623910496633323</v>
       </c>
     </row>
     <row r="65" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C65" t="s">
         <v>31</v>
       </c>
       <c r="D65">
-        <v>0.55551639059787539</v>
+        <v>0.58178761271698543</v>
       </c>
       <c r="N65" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="O65">
-        <v>0.20398208507028392</v>
+        <v>0.18325313896170117</v>
       </c>
       <c r="Q65" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R65" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S65" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T65">
-        <v>0.20398208507028392</v>
+        <v>0.18325313896170117</v>
       </c>
     </row>
     <row r="66" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C66" t="s">
         <v>31</v>
       </c>
       <c r="D66">
-        <v>0.55623118099089208</v>
+        <v>0.5866341308507097</v>
       </c>
       <c r="N66" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O66">
-        <v>0.20243916112641655</v>
+        <v>0.17969540086196575</v>
       </c>
       <c r="Q66" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R66" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S66" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T66">
-        <v>0.20243916112641655</v>
+        <v>0.17969540086196575</v>
       </c>
     </row>
     <row r="67" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C67" t="s">
         <v>31</v>
       </c>
       <c r="D67">
-        <v>0.55020154703806012</v>
+        <v>0.5828476915200943</v>
       </c>
       <c r="N67" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="O67">
-        <v>0.21107823333522024</v>
+        <v>0.18205788996152056</v>
       </c>
       <c r="Q67" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="R67" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S67" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T67">
-        <v>0.21107823333522024</v>
+        <v>0.18205788996152056</v>
       </c>
     </row>
     <row r="68" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C68" t="s">
         <v>31</v>
       </c>
       <c r="D68">
-        <v>0.54795264776358088</v>
+        <v>0.57853416452029405</v>
       </c>
       <c r="N68" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="O68">
-        <v>0.2137588462693471</v>
+        <v>0.19068508634923051</v>
       </c>
       <c r="Q68" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="R68" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S68" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T68">
-        <v>0.2137588462693471</v>
+        <v>0.19068508634923051</v>
       </c>
     </row>
     <row r="69" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C69" t="s">
         <v>31</v>
       </c>
       <c r="D69">
-        <v>0.55097711593261756</v>
+        <v>0.57854174482849485</v>
       </c>
       <c r="N69" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O69">
-        <v>0.20960151601678464</v>
+        <v>0.1903776796021294</v>
       </c>
       <c r="Q69" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="R69" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S69" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T69">
-        <v>0.20960151601678464</v>
+        <v>0.1903776796021294</v>
       </c>
     </row>
     <row r="70" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C70" t="s">
         <v>31</v>
       </c>
       <c r="D70">
-        <v>0.55398382574084237</v>
+        <v>0.59259673395283119</v>
       </c>
       <c r="N70" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O70">
-        <v>0.20626977622864553</v>
+        <v>0.16933192585078385</v>
       </c>
       <c r="Q70" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="R70" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S70" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T70">
-        <v>0.20626977622864553</v>
+        <v>0.16933192585078385</v>
       </c>
     </row>
     <row r="71" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C71" t="s">
         <v>31</v>
       </c>
       <c r="D71">
-        <v>0.55809395289163943</v>
+        <v>0.59733616175560877</v>
       </c>
       <c r="N71" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O71">
-        <v>0.20627767430077357</v>
+        <v>0.16663922759427299</v>
       </c>
       <c r="Q71" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="R71" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S71" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T71">
-        <v>0.20627767430077357</v>
+        <v>0.16663922759427299</v>
       </c>
     </row>
     <row r="72" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C72" t="s">
         <v>31</v>
       </c>
       <c r="D72">
-        <v>0.55684262343842428</v>
+        <v>0.59670327518028043</v>
       </c>
       <c r="N72" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="O72">
-        <v>0.21240700996779904</v>
+        <v>0.17048401088323273</v>
       </c>
       <c r="Q72" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="R72" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S72" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T72">
-        <v>0.21240700996779904</v>
+        <v>0.17048401088323273</v>
       </c>
     </row>
     <row r="73" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C73" t="s">
         <v>31</v>
       </c>
       <c r="D73">
-        <v>0.56529665867494105</v>
+        <v>0.59511742520156963</v>
       </c>
       <c r="N73" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="O73">
-        <v>0.20647519132906678</v>
+        <v>0.17031939745981775</v>
       </c>
       <c r="Q73" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="R73" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S73" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T73">
-        <v>0.20647519132906678</v>
+        <v>0.17031939745981775</v>
       </c>
     </row>
     <row r="74" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C74" t="s">
         <v>31</v>
       </c>
       <c r="D74">
-        <v>0.55551567621283349</v>
+        <v>0.59016223370034759</v>
       </c>
       <c r="N74" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="O74">
-        <v>0.21202852236142658</v>
+        <v>0.17563859817640373</v>
       </c>
       <c r="Q74" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="R74" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S74" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T74">
-        <v>0.21202852236142658</v>
+        <v>0.17563859817640373</v>
       </c>
     </row>
     <row r="75" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C75" t="s">
         <v>31</v>
       </c>
       <c r="D75">
-        <v>0.55194962583772678</v>
+        <v>0.59438245642771403</v>
       </c>
       <c r="N75" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O75">
-        <v>0.19927543450104546</v>
+        <v>0.16989987318385236</v>
       </c>
       <c r="Q75" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="R75" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S75" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T75">
-        <v>0.19927543450104546</v>
+        <v>0.16989987318385236</v>
       </c>
     </row>
     <row r="76" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B76" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C76" t="s">
         <v>31</v>
       </c>
       <c r="D76">
-        <v>0.55309510083104685</v>
+        <v>0.59425969896438258</v>
       </c>
       <c r="N76" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="O76">
-        <v>0.20157171439778296</v>
+        <v>0.17113614006907063</v>
       </c>
       <c r="Q76" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="R76" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S76" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T76">
-        <v>0.20157171439778296</v>
+        <v>0.17113614006907063</v>
       </c>
     </row>
     <row r="77" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C77" t="s">
         <v>31</v>
       </c>
       <c r="D77">
-        <v>0.54542459004524535</v>
+        <v>0.58719805223359456</v>
       </c>
       <c r="N77" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="O77">
-        <v>0.21509647709466082</v>
+        <v>0.17640893579198899</v>
       </c>
       <c r="Q77" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="R77" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S77" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T77">
-        <v>0.21509647709466082</v>
+        <v>0.17640893579198899</v>
       </c>
     </row>
     <row r="78" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C78" t="s">
         <v>31</v>
       </c>
       <c r="D78">
-        <v>0.54721007843195546</v>
+        <v>0.58953923966932587</v>
       </c>
       <c r="N78" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O78">
-        <v>0.20954437456671571</v>
+        <v>0.17539527332512203</v>
       </c>
       <c r="Q78" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="R78" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S78" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T78">
-        <v>0.20954437456671571</v>
+        <v>0.17539527332512203</v>
       </c>
     </row>
     <row r="79" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C79" t="s">
         <v>31</v>
       </c>
       <c r="D79">
-        <v>0.54500689263221247</v>
+        <v>0.58495089236992726</v>
       </c>
       <c r="N79" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O79">
-        <v>0.20683031489671039</v>
+        <v>0.17568100483538487</v>
       </c>
       <c r="Q79" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="R79" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S79" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T79">
-        <v>0.20683031489671039</v>
+        <v>0.17568100483538487</v>
       </c>
     </row>
     <row r="80" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B80" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C80" t="s">
         <v>31</v>
       </c>
       <c r="D80">
-        <v>0.54776461619830064</v>
+        <v>0.58394871613571975</v>
       </c>
       <c r="N80" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O80">
-        <v>0.20401803354297929</v>
+        <v>0.17616617383983338</v>
       </c>
       <c r="Q80" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="R80" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S80" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T80">
-        <v>0.20401803354297929</v>
+        <v>0.17616617383983338</v>
       </c>
     </row>
     <row r="81" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C81" t="s">
         <v>31</v>
       </c>
       <c r="D81">
-        <v>0.53746853512714499</v>
+        <v>0.58076594652903457</v>
       </c>
       <c r="N81" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O81">
-        <v>0.21928550556037243</v>
+        <v>0.18071553701274617</v>
       </c>
       <c r="Q81" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="R81" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S81" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T81">
-        <v>0.21928550556037243</v>
+        <v>0.18071553701274617</v>
       </c>
     </row>
     <row r="82" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C82" t="s">
         <v>31</v>
       </c>
       <c r="D82">
-        <v>0.53997569780802246</v>
+        <v>0.58184404892239017</v>
       </c>
       <c r="N82" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O82">
-        <v>0.210239599971346</v>
+        <v>0.18263853341695269</v>
       </c>
       <c r="Q82" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="R82" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S82" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T82">
-        <v>0.210239599971346</v>
+        <v>0.18263853341695269</v>
       </c>
     </row>
     <row r="83" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C83" t="s">
         <v>31</v>
       </c>
       <c r="D83">
-        <v>0.54154527961424603</v>
+        <v>0.57765804322459791</v>
       </c>
       <c r="N83" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="O83">
-        <v>0.21122544381455668</v>
+        <v>0.18778898110857273</v>
       </c>
       <c r="Q83" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="R83" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S83" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T83">
-        <v>0.21122544381455668</v>
+        <v>0.18778898110857273</v>
       </c>
     </row>
     <row r="84" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B84" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C84" t="s">
         <v>31</v>
       </c>
       <c r="D84">
-        <v>0.5580870319355411</v>
+        <v>0.57531818504147492</v>
       </c>
       <c r="N84" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="O84">
-        <v>0.19603055160612762</v>
+        <v>0.1951247841289781</v>
       </c>
       <c r="Q84" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="R84" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S84" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T84">
-        <v>0.19603055160612762</v>
+        <v>0.1951247841289781</v>
       </c>
     </row>
     <row r="85" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C85" t="s">
         <v>31</v>
       </c>
       <c r="D85">
-        <v>0.54828891283051528</v>
+        <v>0.57490988281217548</v>
       </c>
       <c r="N85" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="O85">
-        <v>0.2016930059426765</v>
+        <v>0.19881688902117681</v>
       </c>
       <c r="Q85" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="R85" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S85" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T85">
-        <v>0.2016930059426765</v>
+        <v>0.19881688902117681</v>
       </c>
     </row>
     <row r="86" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B86" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C86" t="s">
         <v>31</v>
       </c>
       <c r="D86">
-        <v>0.56170476515392986</v>
+        <v>0.57843690438737794</v>
       </c>
       <c r="N86" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O86">
-        <v>0.20256282199704187</v>
+        <v>0.18427272085640367</v>
       </c>
       <c r="Q86" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="R86" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S86" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T86">
-        <v>0.20256282199704187</v>
+        <v>0.18427272085640367</v>
       </c>
     </row>
     <row r="87" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C87" t="s">
         <v>31</v>
       </c>
       <c r="D87">
-        <v>0.54507569702738723</v>
+        <v>0.58306588409796456</v>
       </c>
       <c r="N87" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="O87">
-        <v>0.21247768119982638</v>
+        <v>0.17798373074086279</v>
       </c>
       <c r="Q87" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="R87" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S87" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T87">
-        <v>0.21247768119982638</v>
+        <v>0.17798373074086279</v>
       </c>
     </row>
     <row r="88" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B88" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C88" t="s">
         <v>31</v>
       </c>
       <c r="D88">
-        <v>0.54900384378095357</v>
+        <v>0.58252029131071248</v>
       </c>
       <c r="N88" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="O88">
-        <v>0.21290953064751997</v>
+        <v>0.17922080363434031</v>
       </c>
       <c r="Q88" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="R88" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S88" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T88">
-        <v>0.21290953064751997</v>
+        <v>0.17922080363434031</v>
       </c>
     </row>
     <row r="89" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C89" t="s">
         <v>31</v>
       </c>
       <c r="D89">
-        <v>0.48310975095557074</v>
+        <v>0.42029959114056492</v>
       </c>
       <c r="N89" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="O89">
-        <v>0.23838193337523284</v>
+        <v>0.27021347998671175</v>
       </c>
       <c r="Q89" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="R89" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S89" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T89">
-        <v>0.14078335598326627</v>
+        <v>9.375603651249631E-2</v>
       </c>
     </row>
     <row r="90" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B90" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C90" t="s">
         <v>31</v>
       </c>
       <c r="D90">
-        <v>0.4579416193786407</v>
+        <v>0.39402153361480147</v>
       </c>
       <c r="N90" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O90">
-        <v>0.26608878220864562</v>
+        <v>0.24674943253627049</v>
       </c>
       <c r="Q90" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="R90" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S90" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T90">
-        <v>0.1629374094014864</v>
+        <v>0.10733442833495796</v>
       </c>
     </row>
     <row r="91" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C91" t="s">
         <v>31</v>
       </c>
       <c r="D91">
-        <v>0.43352670575561603</v>
+        <v>0.37357368598976826</v>
       </c>
       <c r="N91" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="O91">
-        <v>0.23984664691779711</v>
+        <v>0.27478781744805242</v>
       </c>
       <c r="Q91" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="R91" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S91" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T91">
-        <v>0.14746427814990898</v>
+        <v>0.12384076438805439</v>
       </c>
     </row>
     <row r="92" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C92" t="s">
         <v>31</v>
       </c>
       <c r="D92">
-        <v>0.40965370962778652</v>
+        <v>0.31456846741732342</v>
       </c>
       <c r="N92" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="O92">
-        <v>0.2625479542764016</v>
+        <v>0.31012898315762444</v>
       </c>
       <c r="Q92" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="R92" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S92" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T92">
-        <v>0.13220967888668614</v>
+        <v>0.11188582204326829</v>
       </c>
     </row>
     <row r="93" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B93" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C93" t="s">
         <v>31</v>
       </c>
       <c r="D93">
-        <v>0.41809568699775401</v>
+        <v>0.32912800102053691</v>
       </c>
       <c r="N93" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="O93">
-        <v>0.25778681539150944</v>
+        <v>0.28072959328466279</v>
       </c>
       <c r="Q93" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="R93" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S93" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T93">
-        <v>0.12543643557309017</v>
+        <v>0.16679732633036745</v>
       </c>
     </row>
     <row r="94" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B94" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C94" t="s">
         <v>31</v>
       </c>
       <c r="D94">
-        <v>0.37122160096092532</v>
+        <v>0.35416356225122941</v>
       </c>
       <c r="N94" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="O94">
-        <v>0.26992243696561175</v>
+        <v>0.30688241817708484</v>
       </c>
       <c r="Q94" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="R94" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S94" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T94">
-        <v>0.12169742383596933</v>
+        <v>0.13155153530486854</v>
       </c>
     </row>
     <row r="95" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B95" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C95" t="s">
         <v>31</v>
       </c>
       <c r="D95">
-        <v>0.3520478291625454</v>
+        <v>0.35942738095437798</v>
       </c>
       <c r="N95" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O95">
-        <v>0.28797953183887987</v>
+        <v>0.26229860480400691</v>
       </c>
       <c r="Q95" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="R95" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S95" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T95">
-        <v>0.10260323079856037</v>
+        <v>0.11504259281442546</v>
       </c>
     </row>
     <row r="96" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B96" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C96" t="s">
         <v>31</v>
       </c>
       <c r="D96">
-        <v>0.39028302636937101</v>
+        <v>0.32913776489136576</v>
       </c>
       <c r="N96" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O96">
-        <v>0.28583656020481141</v>
+        <v>0.33012096723701462</v>
       </c>
       <c r="Q96" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="R96" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S96" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T96">
-        <v>0.12470023860681936</v>
+        <v>9.6930442448614804E-2</v>
       </c>
     </row>
     <row r="97" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C97" t="s">
         <v>31</v>
       </c>
       <c r="D97">
-        <v>0.34809479435492141</v>
+        <v>0.33689179474430331</v>
       </c>
       <c r="N97" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="O97">
-        <v>0.31851085389061168</v>
+        <v>0.31370980458705994</v>
       </c>
       <c r="Q97" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="R97" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S97" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T97">
-        <v>0.1052073237591109</v>
+        <v>0.14559519282898231</v>
       </c>
     </row>
     <row r="98" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B98" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C98" t="s">
         <v>31</v>
       </c>
       <c r="D98">
-        <v>0.37076859362312536</v>
+        <v>0.30834613571675884</v>
       </c>
       <c r="N98" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O98">
-        <v>0.32456596343262467</v>
+        <v>0.31525362456711636</v>
       </c>
       <c r="Q98" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="R98" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S98" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T98">
-        <v>8.952456131758231E-2</v>
+        <v>0.11122780192995303</v>
       </c>
     </row>
     <row r="99" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C99" t="s">
         <v>31</v>
       </c>
       <c r="D99">
-        <v>0.36298370073251079</v>
+        <v>0.42780648659312875</v>
       </c>
       <c r="N99" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="O99">
-        <v>0.31202587201162457</v>
+        <v>0.27147555946986207</v>
       </c>
       <c r="Q99" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="R99" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S99" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T99">
-        <v>9.5075372626086063E-2</v>
+        <v>0.14374907839308126</v>
       </c>
     </row>
     <row r="100" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B100" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C100" t="s">
         <v>31</v>
       </c>
       <c r="D100">
-        <v>0.37047760232479754</v>
+        <v>0.41772783760772009</v>
       </c>
       <c r="N100" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O100">
-        <v>0.30744013848036494</v>
+        <v>0.25535901354785129</v>
       </c>
       <c r="Q100" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="R100" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S100" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T100">
-        <v>0.11926420475863508</v>
+        <v>0.11833553716009758</v>
       </c>
     </row>
     <row r="101" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C101" t="s">
         <v>31</v>
       </c>
       <c r="D101">
-        <v>0.34891785766864558</v>
+        <v>0.39981510372789741</v>
       </c>
       <c r="N101" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="O101">
-        <v>0.25900479475488924</v>
+        <v>0.30129753391177405</v>
       </c>
       <c r="Q101" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="R101" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S101" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T101">
-        <v>9.4903595487187659E-2</v>
+        <v>0.14232524494408361</v>
       </c>
     </row>
     <row r="102" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B102" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C102" t="s">
         <v>31</v>
       </c>
       <c r="D102">
-        <v>0.33800157726617808</v>
+        <v>0.42918752769015794</v>
       </c>
       <c r="N102" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O102">
-        <v>0.37835299764384056</v>
+        <v>0.26749340182495596</v>
       </c>
       <c r="Q102" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="R102" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S102" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T102">
-        <v>0.11682027047486203</v>
+        <v>0.17180444894549013</v>
       </c>
     </row>
     <row r="103" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B103" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C103" t="s">
         <v>31</v>
       </c>
       <c r="D103">
-        <v>0.34094094781778228</v>
+        <v>0.43998483983732639</v>
       </c>
       <c r="N103" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="O103">
-        <v>0.25600939212955481</v>
+        <v>0.27796130038602912</v>
       </c>
       <c r="Q103" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="R103" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S103" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T103">
-        <v>0.11888515749803488</v>
+        <v>0.17731524298147347</v>
       </c>
     </row>
     <row r="104" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B104" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C104" t="s">
         <v>31</v>
       </c>
       <c r="D104">
-        <v>0.28638278493305669</v>
+        <v>0.26610201788154569</v>
       </c>
       <c r="N104" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="O104">
-        <v>0.49754600297983043</v>
+        <v>0.48495670610005093</v>
       </c>
       <c r="Q104" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="R104" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S104" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T104">
-        <v>0.16368484461267899</v>
+        <v>0.20687415019087005</v>
       </c>
     </row>
     <row r="105" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B105" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C105" t="s">
         <v>31</v>
       </c>
       <c r="D105">
-        <v>0.33686080154400028</v>
+        <v>0.27055361217973467</v>
       </c>
       <c r="N105" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="O105">
-        <v>0.36862148062208216</v>
+        <v>0.46939268168147252</v>
       </c>
       <c r="Q105" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="R105" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S105" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T105">
-        <v>0.15120003323308623</v>
+        <v>0.17719011909706472</v>
       </c>
     </row>
     <row r="106" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B106" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C106" t="s">
         <v>31</v>
       </c>
       <c r="D106">
-        <v>0.29201161006866649</v>
+        <v>0.3125340018340903</v>
       </c>
       <c r="N106" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="O106">
-        <v>0.48244662934459864</v>
+        <v>0.36513036248202435</v>
       </c>
       <c r="Q106" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="R106" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S106" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T106">
-        <v>0.10950924132182067</v>
+        <v>0.2124688079611384</v>
       </c>
     </row>
     <row r="107" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B107" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C107" t="s">
         <v>31</v>
       </c>
       <c r="D107">
-        <v>0.39226567190398592</v>
+        <v>0.31899672148051567</v>
       </c>
       <c r="N107" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O107">
-        <v>0.2338955937245337</v>
+        <v>0.25015176325345795</v>
       </c>
       <c r="Q107" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="R107" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S107" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T107">
-        <v>0.12045119399092502</v>
+        <v>0.15044122518348932</v>
       </c>
     </row>
     <row r="108" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B108" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C108" t="s">
         <v>31</v>
       </c>
       <c r="D108">
-        <v>0.43572172942990633</v>
+        <v>0.30897074696094989</v>
       </c>
       <c r="N108" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O108">
-        <v>0.2929874039573796</v>
+        <v>0.37800084581281618</v>
       </c>
       <c r="Q108" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="R108" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S108" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T108">
-        <v>8.9897596794944273E-2</v>
+        <v>0.15322564912638512</v>
       </c>
     </row>
     <row r="109" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B109" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C109" t="s">
         <v>31</v>
       </c>
       <c r="D109">
-        <v>0.40929367381267084</v>
+        <v>0.30645756051241485</v>
       </c>
       <c r="N109" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="O109">
-        <v>0.29963588632227972</v>
+        <v>0.27330241617888601</v>
       </c>
       <c r="Q109" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="R109" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S109" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T109">
-        <v>0.10921752230629392</v>
+        <v>0.20789202013133851</v>
       </c>
     </row>
     <row r="110" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B110" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C110" t="s">
         <v>31</v>
       </c>
       <c r="D110">
-        <v>0.45319256010875864</v>
+        <v>0.37554780353529793</v>
       </c>
       <c r="N110" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O110">
-        <v>0.25548393552158194</v>
+        <v>0.29256189898646384</v>
       </c>
       <c r="Q110" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="R110" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S110" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T110">
-        <v>0.12389428178697201</v>
+        <v>0.17088375159756236</v>
       </c>
     </row>
     <row r="111" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B111" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C111" t="s">
         <v>31</v>
       </c>
       <c r="D111">
-        <v>0.4609760758109368</v>
+        <v>0.34883018974821112</v>
       </c>
       <c r="N111" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="O111">
-        <v>0.26880230412936773</v>
+        <v>0.21138014477808156</v>
       </c>
       <c r="Q111" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="R111" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S111" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T111">
-        <v>0.1301966736345907</v>
+        <v>0.14672826476449422</v>
       </c>
     </row>
     <row r="112" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C112" t="s">
         <v>31</v>
       </c>
       <c r="D112">
-        <v>0.46587406249053392</v>
+        <v>0.35999729369535316</v>
       </c>
       <c r="N112" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="O112">
-        <v>0.28329749273496568</v>
+        <v>0.24691047239625472</v>
       </c>
       <c r="Q112" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="R112" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S112" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T112">
-        <v>0.17091566975864755</v>
+        <v>0.14969993661375014</v>
       </c>
     </row>
     <row r="113" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B113" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C113" t="s">
         <v>31</v>
       </c>
       <c r="D113">
-        <v>0.45889873368718082</v>
+        <v>0.4159246077021676</v>
       </c>
       <c r="N113" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="O113">
-        <v>0.14078335598326627</v>
+        <v>9.5367483868263478E-2</v>
       </c>
       <c r="Q113" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="R113" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S113" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T113">
-        <v>9.580103349238836E-2</v>
+        <v>0.20650912860411808</v>
       </c>
     </row>
     <row r="114" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B114" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C114" t="s">
         <v>31</v>
       </c>
       <c r="D114">
-        <v>0.48400553805664043</v>
+        <v>0.37519248207894423</v>
       </c>
       <c r="N114" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O114">
-        <v>0.1629374094014864</v>
+        <v>0.10940879355415789</v>
       </c>
       <c r="Q114" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="R114" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S114" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T114">
-        <v>0.10846329842999999</v>
+        <v>0.14985648087079029</v>
       </c>
     </row>
     <row r="115" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C115" t="s">
         <v>31</v>
       </c>
       <c r="D115">
-        <v>0.45714632178167292</v>
+        <v>0.39165065099688517</v>
       </c>
       <c r="N115" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="O115">
-        <v>0.14746427814990898</v>
+        <v>0.12536100821765656</v>
       </c>
       <c r="Q115" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="R115" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S115" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T115">
-        <v>0.15631409969054591</v>
+        <v>0.23799112700409911</v>
       </c>
     </row>
     <row r="116" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B116" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C116" t="s">
         <v>31</v>
       </c>
       <c r="D116">
-        <v>0.47228100101925691</v>
+        <v>0.36830935900240208</v>
       </c>
       <c r="N116" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O116">
-        <v>0.13220967888668614</v>
+        <v>0.11380175953149782</v>
       </c>
       <c r="Q116" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="R116" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S116" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T116">
-        <v>0.10408877471279347</v>
+        <v>0.20941476304600548</v>
       </c>
     </row>
     <row r="117" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B117" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C117" t="s">
         <v>31</v>
       </c>
       <c r="D117">
-        <v>0.47053213657346693</v>
+        <v>0.36351872159908627</v>
       </c>
       <c r="N117" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O117">
-        <v>0.12543643557309017</v>
+        <v>0.16857873069179508</v>
       </c>
       <c r="Q117" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="R117" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S117" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T117">
-        <v>0.13501301762343976</v>
+        <v>9.0312498956713116E-2</v>
       </c>
     </row>
     <row r="118" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B118" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C118" t="s">
         <v>31</v>
       </c>
       <c r="D118">
-        <v>0.44679658701108199</v>
+        <v>0.36697885002164504</v>
       </c>
       <c r="N118" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O118">
-        <v>0.12169742383596933</v>
+        <v>0.13377142100472458</v>
       </c>
       <c r="Q118" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="R118" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S118" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T118">
-        <v>0.19860930651924144</v>
+        <v>0.1634789680389313</v>
       </c>
     </row>
     <row r="119" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B119" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C119" t="s">
         <v>31</v>
       </c>
       <c r="D119">
-        <v>0.46900129987117228</v>
+        <v>0.38231494231018531</v>
       </c>
       <c r="N119" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O119">
-        <v>0.10260323079856037</v>
+        <v>0.11703278927621052</v>
       </c>
       <c r="Q119" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="R119" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S119" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T119">
-        <v>0.1291252293293407</v>
+        <v>0.22187176815315762</v>
       </c>
     </row>
     <row r="120" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B120" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C120" t="s">
         <v>31</v>
       </c>
       <c r="D120">
-        <v>0.45721296472445683</v>
+        <v>0.42881391646730799</v>
       </c>
       <c r="N120" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="O120">
-        <v>0.12470023860681936</v>
+        <v>9.9109813283470544E-2</v>
       </c>
       <c r="Q120" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="R120" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S120" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T120">
-        <v>0.10404889590952197</v>
+        <v>0.2768864115740689</v>
       </c>
     </row>
     <row r="121" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B121" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C121" t="s">
         <v>31</v>
       </c>
       <c r="D121">
-        <v>0.43446277604220135</v>
+        <v>0.3872580457637374</v>
       </c>
       <c r="N121" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="O121">
-        <v>0.1052073237591109</v>
+        <v>0.14735074868463904</v>
       </c>
       <c r="Q121" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="R121" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S121" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T121">
-        <v>0.15484385701715817</v>
+        <v>0.2049152579800945</v>
       </c>
     </row>
     <row r="122" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B122" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C122" t="s">
         <v>31</v>
       </c>
       <c r="D122">
-        <v>0.492642283396522</v>
+        <v>0.38887697080015138</v>
       </c>
       <c r="N122" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O122">
-        <v>8.952456131758231E-2</v>
+        <v>0.11315819393754259</v>
       </c>
       <c r="Q122" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="R122" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S122" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T122">
-        <v>0.19994837677786259</v>
+        <v>0.13675200902929974</v>
       </c>
     </row>
     <row r="123" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B123" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C123" t="s">
         <v>31</v>
       </c>
       <c r="D123">
-        <v>0.48307034735515797</v>
+        <v>0.37787272568358093</v>
       </c>
       <c r="N123" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="O123">
-        <v>9.5075372626086063E-2</v>
+        <v>0.14609799689669584</v>
       </c>
       <c r="Q123" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="R123" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S123" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T123">
-        <v>0.16552034536978003</v>
+        <v>0.14142316000503963</v>
       </c>
     </row>
     <row r="124" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B124" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C124" t="s">
         <v>31</v>
       </c>
       <c r="D124">
-        <v>0.43127983008968079</v>
+        <v>0.39357929704030786</v>
       </c>
       <c r="N124" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="O124">
-        <v>0.11926420475863508</v>
+        <v>0.12032441214698447</v>
       </c>
       <c r="Q124" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="R124" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S124" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T124">
-        <v>0.23103688840439254</v>
+        <v>0.13296534741652627</v>
       </c>
     </row>
     <row r="125" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B125" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C125" t="s">
         <v>31</v>
       </c>
       <c r="D125">
-        <v>0.484010732437547</v>
+        <v>0.35208796630369243</v>
       </c>
       <c r="N125" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="O125">
-        <v>9.4903595487187659E-2</v>
+        <v>0.14559235615595523</v>
       </c>
       <c r="Q125" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="R125" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S125" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T125">
-        <v>0.16023957906557712</v>
+        <v>0.14043254637278474</v>
       </c>
     </row>
     <row r="126" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B126" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C126" t="s">
         <v>31</v>
       </c>
       <c r="D126">
-        <v>0.42504066994477419</v>
+        <v>0.37683506802884104</v>
       </c>
       <c r="N126" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="O126">
-        <v>0.11682027047486203</v>
+        <v>0.17540653895307215</v>
       </c>
       <c r="Q126" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="R126" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S126" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T126">
-        <v>0.18167230441968746</v>
+        <v>0.13731684890536111</v>
       </c>
     </row>
     <row r="127" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C127" t="s">
         <v>31</v>
       </c>
       <c r="D127">
-        <v>0.47744274598576869</v>
+        <v>0.3624581183003186</v>
       </c>
       <c r="N127" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="O127">
-        <v>0.11888515749803488</v>
+        <v>0.1796634304888301</v>
       </c>
       <c r="Q127" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="R127" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S127" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T127">
-        <v>0.12221926930270928</v>
+        <v>0.12267853765640552</v>
       </c>
     </row>
     <row r="128" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B128" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C128" t="s">
         <v>31</v>
       </c>
       <c r="D128">
-        <v>0.46519182771681133</v>
+        <v>0.33162482767118157</v>
       </c>
       <c r="N128" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="O128">
-        <v>0.16368484461267899</v>
+        <v>0.2096735126687464</v>
       </c>
       <c r="Q128" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="R128" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S128" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T128">
-        <v>0.1953652135127722</v>
+        <v>0.15406163534611123</v>
       </c>
     </row>
     <row r="129" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B129" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C129" t="s">
         <v>31</v>
       </c>
       <c r="D129">
-        <v>0.45726734959134824</v>
+        <v>0.34956679242288391</v>
       </c>
       <c r="N129" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="O129">
-        <v>0.15120003323308623</v>
+        <v>0.17937014836312359</v>
       </c>
       <c r="Q129" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="R129" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S129" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T129">
-        <v>0.24806287091630741</v>
+        <v>0.11459439742759209</v>
       </c>
     </row>
     <row r="130" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B130" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C130" t="s">
         <v>31</v>
       </c>
       <c r="D130">
-        <v>0.49208437943905387</v>
+        <v>0.34571742131784189</v>
       </c>
       <c r="N130" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O130">
-        <v>0.10950924132182067</v>
+        <v>0.21604735412529097</v>
       </c>
       <c r="Q130" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="R130" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S130" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T130">
-        <v>0.25436438390291011</v>
+        <v>9.9241689879780756E-2</v>
       </c>
     </row>
     <row r="131" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B131" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C131" t="s">
         <v>31</v>
       </c>
       <c r="D131">
-        <v>0.48828450566752546</v>
+        <v>0.33109530572438434</v>
       </c>
       <c r="N131" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="O131">
-        <v>0.12045119399092502</v>
+        <v>0.15210030142356271</v>
       </c>
       <c r="Q131" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="R131" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S131" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T131">
-        <v>0.15362070614064258</v>
+        <v>0.13777451495900994</v>
       </c>
     </row>
     <row r="132" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B132" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C132" t="s">
         <v>31</v>
       </c>
       <c r="D132">
-        <v>0.50938890654042146</v>
+        <v>0.26971529011150158</v>
       </c>
       <c r="N132" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="O132">
-        <v>8.9897596794944273E-2</v>
+        <v>0.15733050674835711</v>
       </c>
       <c r="Q132" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="R132" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S132" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T132">
-        <v>0.12700774475260068</v>
+        <v>0.10625186728252126</v>
       </c>
     </row>
     <row r="133" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B133" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C133" t="s">
         <v>31</v>
       </c>
       <c r="D133">
-        <v>0.46190430825534678</v>
+        <v>0.27133455923996652</v>
       </c>
       <c r="N133" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="O133">
-        <v>0.10921752230629392</v>
+        <v>0.21101162980590951</v>
       </c>
       <c r="Q133" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="R133" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S133" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T133">
-        <v>0.15584131557479777</v>
+        <v>0.11216515426640497</v>
       </c>
     </row>
     <row r="134" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B134" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C134" t="s">
         <v>31</v>
       </c>
       <c r="D134">
-        <v>0.44909332000690616</v>
+        <v>0.29531777853466867</v>
       </c>
       <c r="N134" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="O134">
-        <v>0.12389428178697201</v>
+        <v>0.17276069192853255</v>
       </c>
       <c r="Q134" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="R134" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S134" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T134">
-        <v>0.16698068570140939</v>
+        <v>0.10781761803606701</v>
       </c>
     </row>
     <row r="135" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B135" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C135" t="s">
         <v>31</v>
       </c>
       <c r="D135">
-        <v>0.44821044793745823</v>
+        <v>0.36274627456748026</v>
       </c>
       <c r="N135" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O135">
-        <v>0.1301966736345907</v>
+        <v>0.1488912679376633</v>
       </c>
       <c r="Q135" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="R135" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S135" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T135">
-        <v>0.24849597951247374</v>
+        <v>9.5290538027921423E-2</v>
       </c>
     </row>
     <row r="136" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B136" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C136" t="s">
         <v>31</v>
       </c>
       <c r="D136">
-        <v>0.44269374608403078</v>
+        <v>0.35809735676105481</v>
       </c>
       <c r="N136" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="O136">
-        <v>0.17091695446505495</v>
+        <v>0.151863143505334</v>
       </c>
       <c r="Q136" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="R136" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S136" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T136">
-        <v>0.29594901249298905</v>
+        <v>0.11810722220930366</v>
       </c>
     </row>
     <row r="137" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B137" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C137" t="s">
         <v>31</v>
       </c>
       <c r="D137">
-        <v>0.46673145953527184</v>
+        <v>0.2752889662880682</v>
       </c>
       <c r="N137" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="O137">
-        <v>9.580103349238836E-2</v>
+        <v>0.21021294371055083</v>
       </c>
       <c r="Q137" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="R137" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S137" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T137">
-        <v>0.15504667568882838</v>
+        <v>0.11972931311748634</v>
       </c>
     </row>
     <row r="138" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B138" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C138" t="s">
         <v>31</v>
       </c>
       <c r="D138">
-        <v>0.43714048601202254</v>
+        <v>0.32451286457224171</v>
       </c>
       <c r="N138" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="O138">
-        <v>0.10846329842999999</v>
+        <v>0.15240108064277455</v>
       </c>
       <c r="Q138" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="R138" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S138" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T138">
-        <v>0.21237997542977519</v>
+        <v>0.12435912073879281</v>
       </c>
     </row>
     <row r="139" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B139" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C139" t="s">
         <v>31</v>
       </c>
       <c r="D139">
-        <v>0.45372786719566111</v>
+        <v>0.38620147282819661</v>
       </c>
       <c r="N139" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="O139">
-        <v>0.15631409969054591</v>
+        <v>0.23934989837535903</v>
       </c>
       <c r="Q139" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="R139" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S139" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T139">
-        <v>0.15109296473144815</v>
+        <v>0.11849691083677397</v>
       </c>
     </row>
     <row r="140" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B140" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C140" t="s">
         <v>31</v>
       </c>
       <c r="D140">
-        <v>0.43457388880905201</v>
+        <v>0.351709344582399</v>
       </c>
       <c r="N140" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="O140">
-        <v>0.10408877471279347</v>
+        <v>0.21091463567971003</v>
       </c>
       <c r="Q140" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="R140" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S140" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T140">
-        <v>0.24123702101707653</v>
+        <v>0.10012903025012236</v>
       </c>
     </row>
     <row r="141" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B141" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C141" t="s">
         <v>31</v>
       </c>
       <c r="D141">
-        <v>0.41366765874419065</v>
+        <v>0.40040336390552683</v>
       </c>
       <c r="N141" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="O141">
-        <v>0.13501301762343976</v>
+        <v>9.1616446012535685E-2</v>
       </c>
       <c r="Q141" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="R141" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S141" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T141">
-        <v>0.18813889806679115</v>
+        <v>9.9160795965616735E-2</v>
       </c>
     </row>
     <row r="142" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B142" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C142" t="s">
         <v>31</v>
       </c>
       <c r="D142">
-        <v>0.37291290144228179</v>
+        <v>0.38098076592077479</v>
       </c>
       <c r="N142" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="O142">
-        <v>0.19860930651924144</v>
+        <v>0.16520704382824142</v>
       </c>
       <c r="Q142" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="R142" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S142" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T142">
-        <v>0.1263880209563355</v>
+        <v>0.12734787119492533</v>
       </c>
     </row>
     <row r="143" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B143" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C143" t="s">
         <v>31</v>
       </c>
       <c r="D143">
-        <v>0.45094098824118528</v>
+        <v>0.33977843806521241</v>
       </c>
       <c r="N143" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="O143">
-        <v>0.1291252293293407</v>
+        <v>0.22483821249264385</v>
       </c>
       <c r="Q143" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="R143" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S143" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T143">
-        <v>0.1787263830102831</v>
+        <v>0.15001636070603908</v>
       </c>
     </row>
     <row r="144" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B144" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C144" t="s">
         <v>31</v>
       </c>
       <c r="D144">
-        <v>0.49589585637213934</v>
+        <v>0.30551730017204376</v>
       </c>
       <c r="N144" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="O144">
-        <v>0.10404889590952197</v>
+        <v>0.27940968897119295</v>
       </c>
       <c r="Q144" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="R144" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S144" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T144">
-        <v>0.16054613951952887</v>
+        <v>0.14845374567578173</v>
       </c>
     </row>
     <row r="145" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B145" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C145" t="s">
         <v>31</v>
       </c>
       <c r="D145">
-        <v>0.43885809956829702</v>
+        <v>0.34030016539647251</v>
       </c>
       <c r="N145" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="O145">
-        <v>0.15484385701715817</v>
+        <v>0.20804542603420842</v>
       </c>
       <c r="Q145" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="R145" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S145" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T145">
-        <v>0.15040476903443364</v>
+        <v>0.13043028108022051</v>
       </c>
     </row>
     <row r="146" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B146" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C146" t="s">
         <v>31</v>
       </c>
       <c r="D146">
-        <v>0.39570457337145348</v>
+        <v>0.32810014076582789</v>
       </c>
       <c r="N146" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="O146">
-        <v>0.19994837677786259</v>
+        <v>0.13847784458518647</v>
       </c>
       <c r="Q146" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="R146" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S146" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T146">
-        <v>0.11261123571429653</v>
+        <v>0.12140953639192779</v>
       </c>
     </row>
     <row r="147" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B147" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C147" t="s">
         <v>31</v>
       </c>
       <c r="D147">
-        <v>0.40110790580917932</v>
+        <v>0.31458304585093366</v>
       </c>
       <c r="N147" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O147">
-        <v>0.16552034536978003</v>
+        <v>0.14403119889880903</v>
       </c>
       <c r="Q147" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="R147" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S147" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T147">
-        <v>9.8895024364813053E-2</v>
+        <v>0.11868820457640994</v>
       </c>
     </row>
     <row r="148" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B148" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C148" t="s">
         <v>31</v>
       </c>
       <c r="D148">
-        <v>0.30060651802777777</v>
+        <v>0.35442777401631087</v>
       </c>
       <c r="N148" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="O148">
-        <v>0.23104823691282633</v>
+        <v>0.1345122710667481</v>
       </c>
       <c r="Q148" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="R148" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S148" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T148">
-        <v>0.11581893995399489</v>
+        <v>0.12784164519055186</v>
       </c>
     </row>
     <row r="149" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B149" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C149" t="s">
         <v>31</v>
       </c>
       <c r="D149">
-        <v>0.30671224263881336</v>
+        <v>0.32700800497304644</v>
       </c>
       <c r="N149" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="O149">
-        <v>0.16026521153993725</v>
+        <v>0.14234216764590574</v>
       </c>
       <c r="Q149" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="R149" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S149" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T149">
-        <v>9.7057362435259795E-2</v>
+        <v>9.3136063685326356E-2</v>
       </c>
     </row>
     <row r="150" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B150" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C150" t="s">
         <v>31</v>
       </c>
       <c r="D150">
-        <v>0.4735048077503955</v>
+        <v>0.34996350882324351</v>
       </c>
       <c r="N150" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O150">
-        <v>0.18167268702412953</v>
+        <v>0.1394204460090748</v>
       </c>
       <c r="Q150" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="R150" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S150" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T150">
-        <v>0.10676142203340173</v>
+        <v>9.7698211063154974E-2</v>
       </c>
     </row>
     <row r="151" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B151" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C151" t="s">
         <v>31</v>
       </c>
       <c r="D151">
-        <v>0.43693839205906315</v>
+        <v>0.35346322215382781</v>
       </c>
       <c r="N151" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="O151">
-        <v>0.12221926930270928</v>
+        <v>0.12467576041796787</v>
       </c>
       <c r="Q151" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="R151" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S151" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T151">
-        <v>0.12670677331306604</v>
+        <v>9.2192124338369305E-2</v>
       </c>
     </row>
     <row r="152" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B152" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C152" t="s">
         <v>31</v>
       </c>
       <c r="D152">
-        <v>0.39666091915516222</v>
+        <v>0.41036297061697613</v>
       </c>
       <c r="N152" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="O152">
-        <v>0.1953652135127722</v>
+        <v>0.15671486275133309</v>
       </c>
       <c r="Q152" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="R152" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S152" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T152">
-        <v>0.26335219358038869</v>
+        <v>9.7682568437017087E-2</v>
       </c>
     </row>
     <row r="153" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B153" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C153" t="s">
         <v>31</v>
       </c>
       <c r="D153">
-        <v>0.35730118466345717</v>
+        <v>0.38922833409848506</v>
       </c>
       <c r="N153" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="O153">
-        <v>0.24806287091630741</v>
+        <v>0.11646989276734129</v>
       </c>
       <c r="Q153" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="R153" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S153" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T153">
-        <v>0.14492174899978372</v>
+        <v>9.9009412334265898E-2</v>
       </c>
     </row>
     <row r="154" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B154" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C154" t="s">
         <v>31</v>
       </c>
       <c r="D154">
-        <v>0.38611456670834154</v>
+        <v>0.38927823172491816</v>
       </c>
       <c r="N154" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="O154">
-        <v>0.25436438390291011</v>
+        <v>0.10070537435369936</v>
       </c>
       <c r="Q154" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="R154" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S154" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T154">
-        <v>0.16221489398207681</v>
+        <v>0.11163069016729205</v>
       </c>
     </row>
     <row r="155" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B155" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C155" t="s">
         <v>31</v>
       </c>
       <c r="D155">
-        <v>0.42867091187196649</v>
+        <v>0.38849526259570033</v>
       </c>
       <c r="N155" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="O155">
-        <v>0.15362070614064258</v>
+        <v>0.1396093591114847</v>
       </c>
       <c r="Q155" t="s">
-        <v>384</v>
+        <v>293</v>
       </c>
       <c r="R155" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S155" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T155">
-        <v>0.21962602902322176</v>
+        <v>0.26842619516453819</v>
       </c>
     </row>
     <row r="156" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B156" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C156" t="s">
         <v>31</v>
       </c>
       <c r="D156">
-        <v>0.4722410442967272</v>
+        <v>0.37731604230950982</v>
       </c>
       <c r="N156" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="O156">
-        <v>0.12700774475260068</v>
+        <v>0.10756546230218471</v>
       </c>
       <c r="Q156" t="s">
         <v>294</v>
       </c>
       <c r="R156" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S156" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T156">
-        <v>0.23838193337523284</v>
+        <v>0.24524177038287201</v>
       </c>
     </row>
     <row r="157" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B157" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C157" t="s">
         <v>31</v>
       </c>
       <c r="D157">
-        <v>0.36137931257803424</v>
+        <v>0.40096742289199244</v>
       </c>
       <c r="N157" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="O157">
-        <v>0.15584131557479777</v>
+        <v>0.11381877767904637</v>
       </c>
       <c r="Q157" t="s">
         <v>295</v>
       </c>
       <c r="R157" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S157" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T157">
-        <v>0.26608878220864562</v>
+        <v>0.27185941508608252</v>
       </c>
     </row>
     <row r="158" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B158" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C158" t="s">
         <v>31</v>
       </c>
       <c r="D158">
-        <v>0.40996754173904054</v>
+        <v>0.38741634887358006</v>
       </c>
       <c r="N158" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="O158">
-        <v>0.16698068570140939</v>
+        <v>0.10928335703881714</v>
       </c>
       <c r="Q158" t="s">
         <v>296</v>
       </c>
       <c r="R158" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S158" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T158">
-        <v>0.23984664691779711</v>
+        <v>0.306364245177774</v>
       </c>
     </row>
     <row r="159" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B159" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C159" t="s">
         <v>31</v>
       </c>
       <c r="D159">
-        <v>0.38240760925602302</v>
+        <v>0.38961164178593732</v>
       </c>
       <c r="N159" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="O159">
-        <v>0.24855521435433839</v>
+        <v>9.776607277811461E-2</v>
       </c>
       <c r="Q159" t="s">
         <v>297</v>
       </c>
       <c r="R159" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S159" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T159">
-        <v>0.2625479542764016</v>
+        <v>0.2780571185573677</v>
       </c>
     </row>
     <row r="160" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B160" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C160" t="s">
         <v>31</v>
       </c>
       <c r="D160">
-        <v>0.34356426766418807</v>
+        <v>0.39845504519819608</v>
       </c>
       <c r="N160" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="O160">
-        <v>0.29594903251185001</v>
+        <v>0.11925841375787853</v>
       </c>
       <c r="Q160" t="s">
         <v>298</v>
       </c>
       <c r="R160" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S160" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T160">
-        <v>0.25778681539150944</v>
+        <v>0.30416574894468029</v>
       </c>
     </row>
     <row r="161" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B161" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C161" t="s">
         <v>31</v>
       </c>
       <c r="D161">
-        <v>0.40410313818967092</v>
+        <v>0.40640310873985336</v>
       </c>
       <c r="N161" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O161">
-        <v>0.15504667568882838</v>
+        <v>0.12119250011458586</v>
       </c>
       <c r="Q161" t="s">
         <v>299</v>
       </c>
       <c r="R161" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S161" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T161">
-        <v>0.26992243696561175</v>
+        <v>0.25976840608371515</v>
       </c>
     </row>
     <row r="162" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B162" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C162" t="s">
         <v>31</v>
       </c>
       <c r="D162">
-        <v>0.30903980663982522</v>
+        <v>0.41765740750557007</v>
       </c>
       <c r="N162" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="O162">
-        <v>0.21240227450782917</v>
+        <v>0.12568807789484007</v>
       </c>
       <c r="Q162" t="s">
         <v>300</v>
       </c>
       <c r="R162" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S162" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T162">
-        <v>0.28797953183887987</v>
+        <v>0.32740398555927536</v>
       </c>
     </row>
     <row r="163" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B163" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C163" t="s">
         <v>31</v>
       </c>
       <c r="D163">
-        <v>0.35783598876587758</v>
+        <v>0.39412226382461207</v>
       </c>
       <c r="N163" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="O163">
-        <v>0.15109296473144815</v>
+        <v>0.11988118787790403</v>
       </c>
       <c r="Q163" t="s">
         <v>301</v>
       </c>
       <c r="R163" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S163" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T163">
-        <v>0.28583656020481141</v>
+        <v>0.31198133961053609</v>
       </c>
     </row>
     <row r="164" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B164" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C164" t="s">
         <v>31</v>
       </c>
       <c r="D164">
-        <v>0.37802468963126679</v>
+        <v>0.37103945575459524</v>
       </c>
       <c r="N164" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="O164">
-        <v>0.24123702101707653</v>
+        <v>0.10156806809160995</v>
       </c>
       <c r="Q164" t="s">
         <v>302</v>
       </c>
       <c r="R164" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S164" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T164">
-        <v>0.31851085389061168</v>
+        <v>0.31276919211171744</v>
       </c>
     </row>
     <row r="165" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B165" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C165" t="s">
         <v>31</v>
       </c>
       <c r="D165">
-        <v>0.37407649029584605</v>
+        <v>0.38960542094307049</v>
       </c>
       <c r="N165" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="O165">
-        <v>0.18813893885248187</v>
+        <v>0.10084620863385446</v>
       </c>
       <c r="Q165" t="s">
         <v>303</v>
       </c>
       <c r="R165" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S165" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T165">
-        <v>0.32456596343262467</v>
+        <v>0.26996823914077833</v>
       </c>
     </row>
     <row r="166" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B166" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C166" t="s">
         <v>31</v>
       </c>
       <c r="D166">
-        <v>0.4123686031852119</v>
+        <v>0.38735308167703275</v>
       </c>
       <c r="N166" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="O166">
-        <v>0.1263880209563355</v>
+        <v>0.12887447759077028</v>
       </c>
       <c r="Q166" t="s">
         <v>304</v>
       </c>
       <c r="R166" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S166" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T166">
-        <v>0.31202587201162457</v>
+        <v>0.25418026899118185</v>
       </c>
     </row>
     <row r="167" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B167" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C167" t="s">
         <v>31</v>
       </c>
       <c r="D167">
-        <v>0.37972586805720265</v>
+        <v>0.40086503244538435</v>
       </c>
       <c r="N167" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="O167">
-        <v>0.1787263830102831</v>
+        <v>0.15167437193087635</v>
       </c>
       <c r="Q167" t="s">
         <v>305</v>
       </c>
       <c r="R167" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S167" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T167">
-        <v>0.30744013848036494</v>
+        <v>0.30002158942469204</v>
       </c>
     </row>
     <row r="168" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B168" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C168" t="s">
         <v>31</v>
       </c>
       <c r="D168">
-        <v>0.37595306802264195</v>
+        <v>0.41043145700226263</v>
       </c>
       <c r="N168" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="O168">
-        <v>0.16054613951952887</v>
+        <v>0.14991329891470276</v>
       </c>
       <c r="Q168" t="s">
         <v>306</v>
       </c>
       <c r="R168" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S168" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T168">
-        <v>0.25900479475488924</v>
+        <v>0.26604412138209738</v>
       </c>
     </row>
     <row r="169" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B169" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C169" t="s">
         <v>31</v>
       </c>
       <c r="D169">
-        <v>0.41378521201291724</v>
+        <v>0.40879363978283173</v>
       </c>
       <c r="N169" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="O169">
-        <v>0.15040476903443364</v>
+        <v>0.1318338496670157</v>
       </c>
       <c r="Q169" t="s">
         <v>307</v>
       </c>
       <c r="R169" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S169" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T169">
-        <v>0.37835299764384056</v>
+        <v>0.27655561042335258</v>
       </c>
     </row>
     <row r="170" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B170" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C170" t="s">
         <v>31</v>
       </c>
       <c r="D170">
-        <v>0.41715419052120267</v>
+        <v>0.41998166882896382</v>
       </c>
       <c r="N170" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="O170">
-        <v>0.11261123571429653</v>
+        <v>0.12276381256151059</v>
       </c>
       <c r="Q170" t="s">
         <v>308</v>
       </c>
       <c r="R170" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S170" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T170">
-        <v>0.25600939212955481</v>
+        <v>0.48171278504599158</v>
       </c>
     </row>
     <row r="171" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B171" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C171" t="s">
         <v>31</v>
       </c>
       <c r="D171">
-        <v>0.45757020265654952</v>
+        <v>0.40369608769160109</v>
       </c>
       <c r="N171" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="O171">
-        <v>9.8895024364813053E-2</v>
+        <v>0.11996172955876917</v>
       </c>
       <c r="Q171" t="s">
         <v>309</v>
       </c>
       <c r="R171" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S171" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T171">
-        <v>0.49754600297983043</v>
+        <v>0.46767699283981562</v>
       </c>
     </row>
     <row r="172" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B172" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C172" t="s">
         <v>31</v>
       </c>
       <c r="D172">
-        <v>0.43171657434893945</v>
+        <v>0.41200390828509093</v>
       </c>
       <c r="N172" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="O172">
-        <v>0.11581893995399489</v>
+        <v>0.12930341110109078</v>
       </c>
       <c r="Q172" t="s">
         <v>310</v>
       </c>
       <c r="R172" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S172" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T172">
-        <v>0.36862148062208216</v>
+        <v>0.36369346526208718</v>
       </c>
     </row>
     <row r="173" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B173" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C173" t="s">
         <v>31</v>
       </c>
       <c r="D173">
-        <v>0.43877770838087743</v>
+        <v>0.4113516220498637</v>
       </c>
       <c r="N173" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="O173">
-        <v>9.7057362435259795E-2</v>
+        <v>9.4577327413921289E-2</v>
       </c>
       <c r="Q173" t="s">
         <v>311</v>
       </c>
       <c r="R173" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S173" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T173">
-        <v>0.48244662934459864</v>
+        <v>0.24693285604725621</v>
       </c>
     </row>
     <row r="174" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B174" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C174" t="s">
         <v>31</v>
       </c>
       <c r="D174">
-        <v>0.46732657741169686</v>
+        <v>0.38495596473669552</v>
       </c>
       <c r="N174" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="O174">
-        <v>0.10676142203340173</v>
+        <v>9.9196459417537172E-2</v>
       </c>
       <c r="Q174" t="s">
         <v>312</v>
       </c>
       <c r="R174" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S174" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T174">
-        <v>0.2338955937245337</v>
+        <v>0.37621493327091471</v>
       </c>
     </row>
     <row r="175" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B175" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C175" t="s">
         <v>31</v>
       </c>
       <c r="D175">
-        <v>0.44510221708464992</v>
+        <v>0.36496435356885004</v>
       </c>
       <c r="N175" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="O175">
-        <v>0.12670677331306604</v>
+        <v>9.4167885519076164E-2</v>
       </c>
       <c r="Q175" t="s">
         <v>313</v>
       </c>
       <c r="R175" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S175" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T175">
-        <v>0.2929874039573796</v>
+        <v>0.27166437687247313</v>
       </c>
     </row>
     <row r="176" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B176" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C176" t="s">
         <v>31</v>
       </c>
       <c r="D176">
-        <v>0.393527477783922</v>
+        <v>0.38566585699376238</v>
       </c>
       <c r="N176" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="O176">
-        <v>0.26335219358038869</v>
+        <v>9.9144002381230251E-2</v>
       </c>
       <c r="Q176" t="s">
         <v>314</v>
       </c>
       <c r="R176" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S176" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T176">
-        <v>0.29963588632227972</v>
+        <v>0.29062228731826178</v>
       </c>
     </row>
     <row r="177" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B177" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C177" t="s">
         <v>31</v>
       </c>
       <c r="D177">
-        <v>0.43366772371044715</v>
+        <v>0.39177997001966691</v>
       </c>
       <c r="N177" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="O177">
-        <v>0.14492174899978372</v>
+        <v>0.10040004588325953</v>
       </c>
       <c r="Q177" t="s">
         <v>315</v>
       </c>
       <c r="R177" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S177" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T177">
-        <v>0.25548393552158194</v>
+        <v>0.21026812272291723</v>
       </c>
     </row>
     <row r="178" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B178" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C178" t="s">
         <v>31</v>
       </c>
       <c r="D178">
-        <v>0.43097401622500103</v>
+        <v>0.36198049280584277</v>
       </c>
       <c r="N178" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="O178">
-        <v>0.16221489398207681</v>
+        <v>0.11348504670022851</v>
       </c>
       <c r="Q178" t="s">
         <v>316</v>
       </c>
       <c r="R178" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S178" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T178">
-        <v>0.26880230412936773</v>
-      </c>
-    </row>
-    <row r="179" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B179" t="s">
-        <v>384</v>
-      </c>
-      <c r="C179" t="s">
-        <v>31</v>
-      </c>
-      <c r="D179">
-        <v>0.39981981945626627</v>
-      </c>
-      <c r="N179" t="s">
-        <v>384</v>
-      </c>
-      <c r="O179">
-        <v>0.21962602902322176</v>
-      </c>
-      <c r="Q179" t="s">
-        <v>317</v>
-      </c>
-      <c r="R179" t="s">
-        <v>392</v>
-      </c>
-      <c r="S179" t="s">
-        <v>393</v>
-      </c>
-      <c r="T179">
-        <v>0.28329749273496568</v>
+        <v>0.24533481135148491</v>
       </c>
     </row>
   </sheetData>
@@ -9275,7 +9228,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32F8E0C8-1A13-4D9B-BE23-EDAF2C18B2A8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12645F12-2CBB-45A9-91F3-33D6D240E85D}">
   <dimension ref="A9:S39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -9302,7 +9255,7 @@
         <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D10" t="s">
         <v>43</v>
@@ -9329,19 +9282,19 @@
         <v>42</v>
       </c>
       <c r="N10" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="P10" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="Q10" t="s">
         <v>42</v>
       </c>
       <c r="R10" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="S10" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
@@ -9355,10 +9308,10 @@
         <v>46</v>
       </c>
       <c r="F11" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="H11" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="I11" t="s">
         <v>46</v>
@@ -9379,15 +9332,15 @@
         <v>37</v>
       </c>
       <c r="R11">
-        <v>0.40393549374487786</v>
+        <v>0.40393549374487797</v>
       </c>
       <c r="S11" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="H12" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="I12" t="s">
         <v>46</v>
@@ -9399,10 +9352,10 @@
         <v>37</v>
       </c>
       <c r="R12">
-        <v>0.39017483580399909</v>
+        <v>0.39017483580399898</v>
       </c>
       <c r="S12" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
@@ -9416,7 +9369,7 @@
         <v>0.420942032765037</v>
       </c>
       <c r="S13" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
@@ -9427,10 +9380,10 @@
         <v>37</v>
       </c>
       <c r="R14">
-        <v>0.46044166666666664</v>
+        <v>0.46044166666666669</v>
       </c>
       <c r="S14" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
@@ -9441,10 +9394,10 @@
         <v>37</v>
       </c>
       <c r="R15">
-        <v>0.44534166666666675</v>
+        <v>0.44534166666666669</v>
       </c>
       <c r="S15" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
@@ -9458,7 +9411,7 @@
         <v>0.43370833333333336</v>
       </c>
       <c r="S16" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="17" spans="16:19" x14ac:dyDescent="0.25">
@@ -9469,10 +9422,10 @@
         <v>37</v>
       </c>
       <c r="R17">
-        <v>0.40334166666666665</v>
+        <v>0.40334166666666671</v>
       </c>
       <c r="S17" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="18" spans="16:19" x14ac:dyDescent="0.25">
@@ -9486,7 +9439,7 @@
         <v>0.38215833333333332</v>
       </c>
       <c r="S18" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="19" spans="16:19" x14ac:dyDescent="0.25">
@@ -9500,7 +9453,7 @@
         <v>0.39528333333333338</v>
       </c>
       <c r="S19" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="20" spans="16:19" x14ac:dyDescent="0.25">
@@ -9514,7 +9467,7 @@
         <v>0.39324999999999993</v>
       </c>
       <c r="S20" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="21" spans="16:19" x14ac:dyDescent="0.25">
@@ -9525,10 +9478,10 @@
         <v>37</v>
       </c>
       <c r="R21">
-        <v>0.3855083333333334</v>
+        <v>0.38550833333333334</v>
       </c>
       <c r="S21" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="22" spans="16:19" x14ac:dyDescent="0.25">
@@ -9539,10 +9492,10 @@
         <v>37</v>
       </c>
       <c r="R22">
-        <v>0.40385833333333343</v>
+        <v>0.40385833333333337</v>
       </c>
       <c r="S22" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="23" spans="16:19" x14ac:dyDescent="0.25">
@@ -9556,7 +9509,7 @@
         <v>0.39671666666666666</v>
       </c>
       <c r="S23" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="24" spans="16:19" x14ac:dyDescent="0.25">
@@ -9570,7 +9523,7 @@
         <v>0.38849166666666668</v>
       </c>
       <c r="S24" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="25" spans="16:19" x14ac:dyDescent="0.25">
@@ -9584,7 +9537,7 @@
         <v>0.38614999999999999</v>
       </c>
       <c r="S25" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="26" spans="16:19" x14ac:dyDescent="0.25">
@@ -9598,7 +9551,7 @@
         <v>0.39253333333333335</v>
       </c>
       <c r="S26" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="27" spans="16:19" x14ac:dyDescent="0.25">
@@ -9612,7 +9565,7 @@
         <v>0.41317500000000001</v>
       </c>
       <c r="S27" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="28" spans="16:19" x14ac:dyDescent="0.25">
@@ -9623,10 +9576,10 @@
         <v>37</v>
       </c>
       <c r="R28">
-        <v>0.38524166666666665</v>
+        <v>0.3852416666666667</v>
       </c>
       <c r="S28" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="29" spans="16:19" x14ac:dyDescent="0.25">
@@ -9640,7 +9593,7 @@
         <v>0.39233333333333337</v>
       </c>
       <c r="S29" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="30" spans="16:19" x14ac:dyDescent="0.25">
@@ -9654,7 +9607,7 @@
         <v>0.33180833333333332</v>
       </c>
       <c r="S30" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="31" spans="16:19" x14ac:dyDescent="0.25">
@@ -9668,7 +9621,7 @@
         <v>0.32300833333333329</v>
       </c>
       <c r="S31" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="32" spans="16:19" x14ac:dyDescent="0.25">
@@ -9682,7 +9635,7 @@
         <v>0.3395083333333333</v>
       </c>
       <c r="S32" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="33" spans="16:19" x14ac:dyDescent="0.25">
@@ -9696,7 +9649,7 @@
         <v>0.33240000000000003</v>
       </c>
       <c r="S33" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="34" spans="16:19" x14ac:dyDescent="0.25">
@@ -9710,7 +9663,7 @@
         <v>0.39241666666666664</v>
       </c>
       <c r="S34" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="35" spans="16:19" x14ac:dyDescent="0.25">
@@ -9721,10 +9674,10 @@
         <v>37</v>
       </c>
       <c r="R35">
-        <v>0.45469166666666666</v>
+        <v>0.45469166666666672</v>
       </c>
       <c r="S35" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="36" spans="16:19" x14ac:dyDescent="0.25">
@@ -9738,7 +9691,7 @@
         <v>0.39891666666666659</v>
       </c>
       <c r="S36" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="37" spans="16:19" x14ac:dyDescent="0.25">
@@ -9752,7 +9705,7 @@
         <v>0.39758333333333334</v>
       </c>
       <c r="S37" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="38" spans="16:19" x14ac:dyDescent="0.25">
@@ -9763,10 +9716,10 @@
         <v>37</v>
       </c>
       <c r="R38">
-        <v>0.39640000000000003</v>
+        <v>0.39639999999999992</v>
       </c>
       <c r="S38" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="39" spans="16:19" x14ac:dyDescent="0.25">
@@ -9780,7 +9733,7 @@
         <v>0.39781666666666665</v>
       </c>
       <c r="S39" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
   </sheetData>
